--- a/econ_module/data/h2bb/region_tables.xlsx
+++ b/econ_module/data/h2bb/region_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oliver\Documents\RUB\01_Projekte\IGC_NRW\Arbeitspakete\IGC_model\econ_module\data\h2bb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B93CD7B-7A6F-4454-BF77-68867C344EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4777CE1D-D930-4231-8A9F-A7B67DD88590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4725" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prices" sheetId="1" r:id="rId1"/>
@@ -163,13 +163,13 @@
     <t>EU-FRA</t>
   </si>
   <si>
-    <t>EU-NDL</t>
-  </si>
-  <si>
     <t>EU-DNK</t>
   </si>
   <si>
     <t>commodity</t>
+  </si>
+  <si>
+    <t>EU-NLD</t>
   </si>
 </sst>
 </file>
@@ -518,7 +518,7 @@
         <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -856,7 +856,7 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -1054,7 +1054,7 @@
         <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -1392,7 +1392,7 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -1584,9 +1584,7 @@
   <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="11" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="23" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="23" width="4.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.35">
@@ -1594,7 +1592,7 @@
         <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -1932,7 +1930,7 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -2022,7 +2020,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>

--- a/econ_module/data/h2bb/region_tables.xlsx
+++ b/econ_module/data/h2bb/region_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oliver\Documents\RUB\01_Projekte\IGC_NRW\Arbeitspakete\IGC_model\econ_module\data\h2bb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA06AE03-254C-49CD-997E-028E025D78FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E52E6B-DCB5-4294-8890-D2E4E8388DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-4725" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prices" sheetId="1" r:id="rId1"/>
@@ -353,9 +353,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -725,7 +726,7 @@
         <v>112</v>
       </c>
       <c r="F2" s="1">
-        <f t="shared" ref="F2:S2" si="0">E2+F$8</f>
+        <f t="shared" ref="F2:L2" si="0">E2+F$8</f>
         <v>115</v>
       </c>
       <c r="G2" s="1">
@@ -792,67 +793,67 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E3" s="1">
         <f t="shared" ref="E3:L3" si="2">D3+E$8</f>
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F3" s="1">
         <f t="shared" si="2"/>
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" si="2"/>
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H3" s="1">
         <f t="shared" si="2"/>
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I3" s="1">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J3" s="1">
         <f t="shared" si="2"/>
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K3" s="1">
         <f t="shared" si="2"/>
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L3" s="1">
         <f t="shared" si="2"/>
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M3" s="1">
         <f t="shared" ref="M3:M6" si="3">D3+M$8</f>
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N3" s="1">
         <f t="shared" ref="N3:S3" si="4">M3+N$8</f>
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O3" s="1">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P3" s="1">
         <f t="shared" si="4"/>
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q3" s="1">
         <f t="shared" si="4"/>
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="S3" s="1">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
@@ -866,67 +867,67 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:L4" si="5">D4+E$8</f>
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F4" s="1">
         <f t="shared" si="5"/>
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G4" s="1">
         <f t="shared" si="5"/>
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H4" s="1">
         <f t="shared" si="5"/>
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I4" s="1">
         <f t="shared" si="5"/>
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J4" s="1">
         <f t="shared" si="5"/>
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K4" s="1">
         <f t="shared" si="5"/>
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L4" s="1">
         <f t="shared" si="5"/>
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="M4" s="1">
         <f t="shared" si="3"/>
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="N4" s="1">
         <f t="shared" ref="N4:S4" si="6">M4+N$8</f>
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="O4" s="1">
         <f t="shared" si="6"/>
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="6"/>
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Q4" s="1">
         <f t="shared" si="6"/>
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="6"/>
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="S4" s="1">
         <f t="shared" si="6"/>
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
@@ -1215,67 +1216,67 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="E2" s="1">
         <f>D2*1.1</f>
-        <v>99.000000000000014</v>
+        <v>143</v>
       </c>
       <c r="F2" s="1">
         <f>D2*1.2</f>
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="G2" s="1">
         <f>D2*1.3</f>
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="H2" s="1">
         <f>D2*1.4</f>
-        <v>125.99999999999999</v>
+        <v>182</v>
       </c>
       <c r="I2" s="1">
         <f>D2*1.5</f>
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="J2" s="1">
         <f>D2*1.6</f>
-        <v>144</v>
+        <v>208</v>
       </c>
       <c r="K2" s="1">
         <f>D2*1.8</f>
-        <v>162</v>
+        <v>234</v>
       </c>
       <c r="L2" s="1">
         <f>D2*2</f>
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="M2" s="1">
         <f>D2*0.9</f>
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="N2" s="1">
         <f>D2*0.8</f>
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="O2" s="1">
         <f>D2*0.7</f>
-        <v>62.999999999999993</v>
+        <v>91</v>
       </c>
       <c r="P2" s="1">
         <f>D2*0.6</f>
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="Q2" s="1">
         <f>D2*0.5</f>
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="R2" s="1">
         <f>D2*0.4</f>
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="S2" s="1">
         <f>D2*0.2</f>
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
@@ -1437,67 +1438,67 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G5" s="1">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="H5" s="1">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="I5" s="1">
         <f t="shared" si="4"/>
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J5" s="1">
         <f t="shared" si="5"/>
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="K5" s="1">
         <f t="shared" si="6"/>
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="L5" s="1">
         <f t="shared" si="7"/>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M5" s="1">
         <f t="shared" si="8"/>
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="N5" s="1">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="O5" s="1">
         <f t="shared" si="10"/>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="P5" s="1">
         <f t="shared" si="11"/>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Q5" s="1">
         <f t="shared" si="12"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="13"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="S5" s="1">
         <f t="shared" si="14"/>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.35">
@@ -1666,66 +1667,66 @@
       <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>90</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <f>D2*1.1</f>
         <v>99.000000000000014</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <f>D2*1.2</f>
         <v>108</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="2">
         <f>D2*1.3</f>
         <v>117</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="2">
         <f>D2*1.4</f>
         <v>125.99999999999999</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="2">
         <f>D2*1.5</f>
         <v>135</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="2">
         <f>D2*1.6</f>
         <v>144</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="2">
         <f>D2*1.8</f>
         <v>162</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="2">
         <f>D2*2</f>
         <v>180</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="2">
         <f>D2*0.9</f>
         <v>81</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="2">
         <f>D2*0.8</f>
         <v>72</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="2">
         <f>D2*0.7</f>
         <v>62.999999999999993</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="2">
         <f>D2*0.6</f>
         <v>54</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <f>D2*0.5</f>
         <v>45</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="2">
         <f>D2*0.4</f>
         <v>36</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="2">
         <f>D2*0.2</f>
         <v>18</v>
       </c>
@@ -1740,66 +1741,66 @@
       <c r="C3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>10</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <f t="shared" ref="E3:E6" si="0">D3*1.1</f>
         <v>11</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <f t="shared" ref="F3:F6" si="1">D3*1.2</f>
         <v>12</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="2">
         <f t="shared" ref="G3:G6" si="2">D3*1.3</f>
         <v>13</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="2">
         <f t="shared" ref="H3:H6" si="3">D3*1.4</f>
         <v>14</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="2">
         <f t="shared" ref="I3:I6" si="4">D3*1.5</f>
         <v>15</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="2">
         <f t="shared" ref="J3:J6" si="5">D3*1.6</f>
         <v>16</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K3" s="2">
         <f t="shared" ref="K3:K6" si="6">D3*1.8</f>
         <v>18</v>
       </c>
-      <c r="L3" s="1">
+      <c r="L3" s="2">
         <f t="shared" ref="L3:L6" si="7">D3*2</f>
         <v>20</v>
       </c>
-      <c r="M3" s="1">
+      <c r="M3" s="2">
         <f t="shared" ref="M3:M6" si="8">D3*0.9</f>
         <v>9</v>
       </c>
-      <c r="N3" s="1">
+      <c r="N3" s="2">
         <f t="shared" ref="N3:N6" si="9">D3*0.8</f>
         <v>8</v>
       </c>
-      <c r="O3" s="1">
+      <c r="O3" s="2">
         <f t="shared" ref="O3:O6" si="10">D3*0.7</f>
         <v>7</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="2">
         <f t="shared" ref="P3:P6" si="11">D3*0.6</f>
         <v>6</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <f t="shared" ref="Q3:Q6" si="12">D3*0.5</f>
         <v>5</v>
       </c>
-      <c r="R3" s="1">
+      <c r="R3" s="2">
         <f t="shared" ref="R3:R6" si="13">D3*0.4</f>
         <v>4</v>
       </c>
-      <c r="S3" s="1">
+      <c r="S3" s="2">
         <f t="shared" ref="S3:S6" si="14">D3*0.2</f>
         <v>2</v>
       </c>
@@ -1814,68 +1815,68 @@
       <c r="C4" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="1">
-        <v>50</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="D4" s="2">
+        <v>80</v>
+      </c>
+      <c r="E4" s="2">
         <f t="shared" si="0"/>
-        <v>55.000000000000007</v>
-      </c>
-      <c r="F4" s="1">
+        <v>88</v>
+      </c>
+      <c r="F4" s="2">
         <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="G4" s="1">
+        <v>96</v>
+      </c>
+      <c r="G4" s="2">
         <f t="shared" si="2"/>
-        <v>65</v>
-      </c>
-      <c r="H4" s="1">
+        <v>104</v>
+      </c>
+      <c r="H4" s="2">
         <f t="shared" si="3"/>
-        <v>70</v>
-      </c>
-      <c r="I4" s="1">
+        <v>112</v>
+      </c>
+      <c r="I4" s="2">
         <f t="shared" si="4"/>
-        <v>75</v>
-      </c>
-      <c r="J4" s="1">
+        <v>120</v>
+      </c>
+      <c r="J4" s="2">
         <f t="shared" si="5"/>
-        <v>80</v>
-      </c>
-      <c r="K4" s="1">
+        <v>128</v>
+      </c>
+      <c r="K4" s="2">
         <f t="shared" si="6"/>
-        <v>90</v>
-      </c>
-      <c r="L4" s="1">
+        <v>144</v>
+      </c>
+      <c r="L4" s="2">
         <f t="shared" si="7"/>
-        <v>100</v>
-      </c>
-      <c r="M4" s="1">
+        <v>160</v>
+      </c>
+      <c r="M4" s="2">
         <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-      <c r="N4" s="1">
+        <v>72</v>
+      </c>
+      <c r="N4" s="2">
         <f t="shared" si="9"/>
+        <v>64</v>
+      </c>
+      <c r="O4" s="2">
+        <f t="shared" si="10"/>
+        <v>56</v>
+      </c>
+      <c r="P4" s="2">
+        <f t="shared" si="11"/>
+        <v>48</v>
+      </c>
+      <c r="Q4" s="2">
+        <f t="shared" si="12"/>
         <v>40</v>
       </c>
-      <c r="O4" s="1">
-        <f t="shared" si="10"/>
-        <v>35</v>
-      </c>
-      <c r="P4" s="1">
-        <f t="shared" si="11"/>
-        <v>30</v>
-      </c>
-      <c r="Q4" s="1">
-        <f t="shared" si="12"/>
-        <v>25</v>
-      </c>
-      <c r="R4" s="1">
+      <c r="R4" s="2">
         <f t="shared" si="13"/>
-        <v>20</v>
-      </c>
-      <c r="S4" s="1">
+        <v>32</v>
+      </c>
+      <c r="S4" s="2">
         <f t="shared" si="14"/>
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
@@ -1888,66 +1889,66 @@
       <c r="C5" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>30</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="2">
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="2">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="2">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="2">
         <f t="shared" si="5"/>
         <v>48</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K5" s="2">
         <f t="shared" si="6"/>
         <v>54</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L5" s="2">
         <f t="shared" si="7"/>
         <v>60</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M5" s="2">
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5" s="2">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="O5" s="1">
+      <c r="O5" s="2">
         <f t="shared" si="10"/>
         <v>21</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="2">
         <f t="shared" si="11"/>
         <v>18</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <f t="shared" si="12"/>
         <v>15</v>
       </c>
-      <c r="R5" s="1">
+      <c r="R5" s="2">
         <f t="shared" si="13"/>
         <v>12</v>
       </c>
-      <c r="S5" s="1">
+      <c r="S5" s="2">
         <f t="shared" si="14"/>
         <v>6</v>
       </c>
@@ -1962,66 +1963,66 @@
       <c r="C6" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="2">
         <v>20</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="2">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="2">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="2">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="2">
         <f t="shared" si="5"/>
         <v>32</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6" s="2">
         <f t="shared" si="6"/>
         <v>36</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L6" s="2">
         <f t="shared" si="7"/>
         <v>40</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M6" s="2">
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6" s="2">
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="O6" s="1">
+      <c r="O6" s="2">
         <f t="shared" si="10"/>
         <v>14</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="2">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <f t="shared" si="12"/>
         <v>10</v>
       </c>
-      <c r="R6" s="1">
+      <c r="R6" s="2">
         <f t="shared" si="13"/>
         <v>8</v>
       </c>
-      <c r="S6" s="1">
+      <c r="S6" s="2">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>

--- a/econ_module/data/h2bb/region_tables.xlsx
+++ b/econ_module/data/h2bb/region_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oliver\Documents\RUB\01_Projekte\IGC_NRW\Arbeitspakete\IGC_model\econ_module\data\h2bb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A1B3B3-ED45-49DA-A973-96FDDA323D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9377282-14BC-453E-8F90-6A0E15122C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4725" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4725" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prices" sheetId="1" r:id="rId1"/>
@@ -755,7 +755,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -833,7 +833,7 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1117,7 +1117,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N161"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
@@ -1127,7 +1127,7 @@
     <col min="10" max="14" width="8.36328125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1182,40 +1182,40 @@
         <v>1</v>
       </c>
       <c r="D2" s="5">
-        <v>51.387999999999998</v>
+        <v>93.665499999999994</v>
       </c>
       <c r="E2" s="5">
-        <v>52.946399999999997</v>
+        <v>84.925600000000003</v>
       </c>
       <c r="F2" s="5">
-        <v>53.441200000000002</v>
+        <v>99.7761</v>
       </c>
       <c r="G2" s="5">
-        <v>54.441499999999998</v>
+        <v>113.47499999999999</v>
       </c>
       <c r="H2" s="5">
-        <v>55.3812</v>
+        <v>91.102000000000004</v>
       </c>
       <c r="I2" s="5">
-        <v>55.694600000000001</v>
+        <v>90.376199999999997</v>
       </c>
       <c r="J2" s="5">
-        <v>51.7973</v>
+        <v>110.57899999999999</v>
       </c>
       <c r="K2" s="5">
-        <v>51.300400000000003</v>
+        <v>83.773899999999998</v>
       </c>
       <c r="L2" s="5">
-        <v>50.531599999999997</v>
+        <v>84.439099999999996</v>
       </c>
       <c r="M2" s="5">
-        <v>49.403199999999998</v>
+        <v>83.897199999999998</v>
       </c>
       <c r="N2" s="5">
-        <v>48.394199999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+        <v>80.798500000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -1226,40 +1226,40 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>83.899699999999996</v>
+        <v>85.782300000000006</v>
       </c>
       <c r="E3" s="5">
-        <v>84.204499999999996</v>
+        <v>52.479100000000003</v>
       </c>
       <c r="F3" s="5">
-        <v>85.298599999999993</v>
+        <v>54.353299999999997</v>
       </c>
       <c r="G3" s="5">
-        <v>86.467299999999994</v>
+        <v>53.960299999999997</v>
       </c>
       <c r="H3" s="5">
-        <v>86.487200000000001</v>
+        <v>170.22900000000001</v>
       </c>
       <c r="I3" s="5">
-        <v>88.052599999999998</v>
+        <v>177.30199999999999</v>
       </c>
       <c r="J3" s="5">
-        <v>82.267300000000006</v>
+        <v>54.2318</v>
       </c>
       <c r="K3" s="5">
-        <v>81.436300000000003</v>
+        <v>86.393900000000002</v>
       </c>
       <c r="L3" s="5">
-        <v>80.105800000000002</v>
+        <v>52.879600000000003</v>
       </c>
       <c r="M3" s="5">
-        <v>79.376300000000001</v>
+        <v>58.589300000000001</v>
       </c>
       <c r="N3" s="5">
-        <v>77.669399999999996</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+        <v>55.413800000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1270,40 +1270,40 @@
         <v>1</v>
       </c>
       <c r="D4" s="5">
-        <v>73.554699999999997</v>
+        <v>105.276</v>
       </c>
       <c r="E4" s="5">
-        <v>75.645799999999994</v>
+        <v>106.58499999999999</v>
       </c>
       <c r="F4" s="5">
-        <v>76.429900000000004</v>
+        <v>107.2</v>
       </c>
       <c r="G4" s="5">
-        <v>77.6143</v>
+        <v>109.315</v>
       </c>
       <c r="H4" s="5">
-        <v>80.520300000000006</v>
+        <v>110.523</v>
       </c>
       <c r="I4" s="5">
-        <v>82.441699999999997</v>
+        <v>112.167</v>
       </c>
       <c r="J4" s="5">
-        <v>73.145399999999995</v>
+        <v>104.051</v>
       </c>
       <c r="K4" s="5">
-        <v>72.249600000000001</v>
+        <v>102.601</v>
       </c>
       <c r="L4" s="5">
-        <v>72.297600000000003</v>
+        <v>101.75700000000001</v>
       </c>
       <c r="M4" s="5">
-        <v>71.215100000000007</v>
+        <v>99.772000000000006</v>
       </c>
       <c r="N4" s="5">
-        <v>69.941800000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+        <v>97.575299999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -1314,40 +1314,40 @@
         <v>1</v>
       </c>
       <c r="D5" s="5">
-        <v>73.490600000000001</v>
+        <v>92.520099999999999</v>
       </c>
       <c r="E5" s="5">
-        <v>74.927099999999996</v>
+        <v>94.477699999999999</v>
       </c>
       <c r="F5" s="5">
-        <v>75.368600000000001</v>
+        <v>95.916600000000003</v>
       </c>
       <c r="G5" s="5">
-        <v>76.048100000000005</v>
+        <v>96.302499999999995</v>
       </c>
       <c r="H5" s="5">
-        <v>76.162599999999998</v>
+        <v>96.682199999999995</v>
       </c>
       <c r="I5" s="5">
-        <v>77.186999999999998</v>
+        <v>144.50200000000001</v>
       </c>
       <c r="J5" s="5">
-        <v>73.779700000000005</v>
+        <v>85.769300000000001</v>
       </c>
       <c r="K5" s="5">
-        <v>73.272199999999998</v>
+        <v>76.986999999999995</v>
       </c>
       <c r="L5" s="5">
-        <v>71.400899999999993</v>
+        <v>87.206100000000006</v>
       </c>
       <c r="M5" s="5">
-        <v>71.483500000000006</v>
+        <v>53.857500000000002</v>
       </c>
       <c r="N5" s="5">
-        <v>70.948599999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+        <v>64.932199999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1358,40 +1358,40 @@
         <v>1</v>
       </c>
       <c r="D6" s="5">
-        <v>73.782600000000002</v>
+        <v>119.357</v>
       </c>
       <c r="E6" s="5">
-        <v>75.228899999999996</v>
+        <v>119.41500000000001</v>
       </c>
       <c r="F6" s="5">
-        <v>76.215199999999996</v>
+        <v>119.524</v>
       </c>
       <c r="G6" s="5">
-        <v>79.032499999999999</v>
+        <v>119.845</v>
       </c>
       <c r="H6" s="5">
-        <v>79.959000000000003</v>
+        <v>120.358</v>
       </c>
       <c r="I6" s="5">
-        <v>80.633300000000006</v>
+        <v>120.227</v>
       </c>
       <c r="J6" s="5">
-        <v>73.372500000000002</v>
+        <v>119.386</v>
       </c>
       <c r="K6" s="5">
-        <v>72.124700000000004</v>
+        <v>118.98699999999999</v>
       </c>
       <c r="L6" s="5">
-        <v>70.279899999999998</v>
+        <v>118.828</v>
       </c>
       <c r="M6" s="5">
-        <v>68.194400000000002</v>
+        <v>113.191</v>
       </c>
       <c r="N6" s="5">
-        <v>65.524000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+        <v>110.17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1402,40 +1402,40 @@
         <v>1</v>
       </c>
       <c r="D7" s="5">
-        <v>71.229900000000001</v>
+        <v>110.804</v>
       </c>
       <c r="E7" s="5">
-        <v>72.776700000000005</v>
+        <v>87.038799999999995</v>
       </c>
       <c r="F7" s="5">
-        <v>71.778999999999996</v>
+        <v>85.471000000000004</v>
       </c>
       <c r="G7" s="5">
-        <v>73.880600000000001</v>
+        <v>109.54300000000001</v>
       </c>
       <c r="H7" s="5">
-        <v>74.7958</v>
+        <v>91.293400000000005</v>
       </c>
       <c r="I7" s="5">
-        <v>75.0732</v>
+        <v>92.774199999999993</v>
       </c>
       <c r="J7" s="5">
-        <v>72.333200000000005</v>
+        <v>110.453</v>
       </c>
       <c r="K7" s="5">
-        <v>71.794600000000003</v>
+        <v>83.29</v>
       </c>
       <c r="L7" s="5">
-        <v>70.316500000000005</v>
+        <v>108.599</v>
       </c>
       <c r="M7" s="5">
-        <v>69.419700000000006</v>
+        <v>110.336</v>
       </c>
       <c r="N7" s="5">
-        <v>67.944800000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+        <v>102.327</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1446,40 +1446,40 @@
         <v>1</v>
       </c>
       <c r="D8" s="5">
-        <v>82.868099999999998</v>
+        <v>89.906899999999993</v>
       </c>
       <c r="E8" s="5">
-        <v>85.126300000000001</v>
+        <v>89.340199999999996</v>
       </c>
       <c r="F8" s="5">
-        <v>86.520499999999998</v>
+        <v>91.280900000000003</v>
       </c>
       <c r="G8" s="5">
-        <v>87.899799999999999</v>
+        <v>131.815</v>
       </c>
       <c r="H8" s="5">
-        <v>90.225700000000003</v>
+        <v>95.937700000000007</v>
       </c>
       <c r="I8" s="5">
-        <v>93.405900000000003</v>
+        <v>97.988200000000006</v>
       </c>
       <c r="J8" s="5">
-        <v>83.479100000000003</v>
+        <v>86.922600000000003</v>
       </c>
       <c r="K8" s="5">
-        <v>83.418599999999998</v>
+        <v>82.974199999999996</v>
       </c>
       <c r="L8" s="5">
-        <v>81.327600000000004</v>
+        <v>117.271</v>
       </c>
       <c r="M8" s="5">
-        <v>79.378399999999999</v>
+        <v>122.813</v>
       </c>
       <c r="N8" s="5">
-        <v>74.769000000000005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+        <v>84.35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>175</v>
       </c>
@@ -1490,40 +1490,40 @@
         <v>1</v>
       </c>
       <c r="D9" s="5">
-        <v>135.46299999999999</v>
+        <v>199.946</v>
       </c>
       <c r="E9" s="5">
-        <v>135.63999999999999</v>
+        <v>201.95400000000001</v>
       </c>
       <c r="F9" s="5">
-        <v>135.78299999999999</v>
+        <v>202.006</v>
       </c>
       <c r="G9" s="5">
-        <v>136.72800000000001</v>
+        <v>203.13900000000001</v>
       </c>
       <c r="H9" s="5">
-        <v>137.75800000000001</v>
+        <v>204.405</v>
       </c>
       <c r="I9" s="5">
-        <v>138.03</v>
+        <v>203.214</v>
       </c>
       <c r="J9" s="5">
-        <v>133.84299999999999</v>
+        <v>200.06</v>
       </c>
       <c r="K9" s="5">
-        <v>133.327</v>
+        <v>200.43299999999999</v>
       </c>
       <c r="L9" s="5">
-        <v>135.28299999999999</v>
+        <v>204.18799999999999</v>
       </c>
       <c r="M9" s="5">
-        <v>135.435</v>
+        <v>172</v>
       </c>
       <c r="N9" s="5">
-        <v>134.44399999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+        <v>105.80800000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1534,40 +1534,40 @@
         <v>1</v>
       </c>
       <c r="D10" s="5">
-        <v>85.460499999999996</v>
+        <v>122.982</v>
       </c>
       <c r="E10" s="5">
-        <v>83.657700000000006</v>
+        <v>123.16800000000001</v>
       </c>
       <c r="F10" s="5">
-        <v>84.864800000000002</v>
+        <v>122.499</v>
       </c>
       <c r="G10" s="5">
-        <v>85.916600000000003</v>
+        <v>122.72199999999999</v>
       </c>
       <c r="H10" s="5">
-        <v>86.6751</v>
+        <v>123.529</v>
       </c>
       <c r="I10" s="5">
-        <v>88.715299999999999</v>
+        <v>123.71299999999999</v>
       </c>
       <c r="J10" s="5">
-        <v>80.412000000000006</v>
+        <v>123.163</v>
       </c>
       <c r="K10" s="5">
-        <v>61.119399999999999</v>
+        <v>123.286</v>
       </c>
       <c r="L10" s="5">
-        <v>69.868499999999997</v>
+        <v>124.45699999999999</v>
       </c>
       <c r="M10" s="5">
-        <v>54.776200000000003</v>
+        <v>124.721</v>
       </c>
       <c r="N10" s="5">
-        <v>64.557000000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+        <v>124.348</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1578,40 +1578,40 @@
         <v>1</v>
       </c>
       <c r="D11" s="5">
-        <v>64.909899999999993</v>
+        <v>107.571</v>
       </c>
       <c r="E11" s="5">
-        <v>66.120500000000007</v>
+        <v>95.095100000000002</v>
       </c>
       <c r="F11" s="5">
-        <v>66.236199999999997</v>
+        <v>100.459</v>
       </c>
       <c r="G11" s="5">
-        <v>67.218699999999998</v>
+        <v>103.227</v>
       </c>
       <c r="H11" s="5">
-        <v>72.056700000000006</v>
+        <v>103.56699999999999</v>
       </c>
       <c r="I11" s="5">
-        <v>73.077500000000001</v>
+        <v>103.824</v>
       </c>
       <c r="J11" s="5">
-        <v>63.997199999999999</v>
+        <v>102.143</v>
       </c>
       <c r="K11" s="5">
-        <v>63.4848</v>
+        <v>94.349900000000005</v>
       </c>
       <c r="L11" s="5">
-        <v>62.321199999999997</v>
+        <v>100.108</v>
       </c>
       <c r="M11" s="5">
-        <v>59.451599999999999</v>
+        <v>101.643</v>
       </c>
       <c r="N11" s="5">
-        <v>58.584899999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+        <v>100.815</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1622,40 +1622,40 @@
         <v>1</v>
       </c>
       <c r="D12" s="5">
-        <v>61.042000000000002</v>
+        <v>113.779</v>
       </c>
       <c r="E12" s="5">
-        <v>62.049199999999999</v>
+        <v>115.73099999999999</v>
       </c>
       <c r="F12" s="5">
-        <v>62.837400000000002</v>
+        <v>117.85299999999999</v>
       </c>
       <c r="G12" s="5">
-        <v>63.572400000000002</v>
+        <v>119.158</v>
       </c>
       <c r="H12" s="5">
-        <v>65.194599999999994</v>
+        <v>119.52</v>
       </c>
       <c r="I12" s="5">
-        <v>67.074200000000005</v>
+        <v>119.336</v>
       </c>
       <c r="J12" s="5">
-        <v>60.968699999999998</v>
+        <v>112.497</v>
       </c>
       <c r="K12" s="5">
-        <v>60.095100000000002</v>
+        <v>111.746</v>
       </c>
       <c r="L12" s="5">
-        <v>58.875999999999998</v>
+        <v>108.08799999999999</v>
       </c>
       <c r="M12" s="5">
-        <v>55.699300000000001</v>
+        <v>106.55</v>
       </c>
       <c r="N12" s="5">
-        <v>52.659500000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+        <v>101.173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1666,40 +1666,40 @@
         <v>1</v>
       </c>
       <c r="D13" s="5">
-        <v>35.120199999999997</v>
+        <v>90.126099999999994</v>
       </c>
       <c r="E13" s="5">
-        <v>35.619599999999998</v>
+        <v>93.383600000000001</v>
       </c>
       <c r="F13" s="5">
-        <v>35.658700000000003</v>
+        <v>93.688400000000001</v>
       </c>
       <c r="G13" s="5">
-        <v>36.166200000000003</v>
+        <v>93.628699999999995</v>
       </c>
       <c r="H13" s="5">
-        <v>36.9711</v>
+        <v>93.712900000000005</v>
       </c>
       <c r="I13" s="5">
-        <v>37.8367</v>
+        <v>93.227699999999999</v>
       </c>
       <c r="J13" s="5">
-        <v>34.755099999999999</v>
+        <v>92.371600000000001</v>
       </c>
       <c r="K13" s="5">
-        <v>33.951900000000002</v>
+        <v>93.131399999999999</v>
       </c>
       <c r="L13" s="5">
-        <v>32.494</v>
+        <v>90.125200000000007</v>
       </c>
       <c r="M13" s="5">
-        <v>28.360499999999998</v>
+        <v>87.811999999999998</v>
       </c>
       <c r="N13" s="5">
-        <v>24.780899999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+        <v>84.738699999999994</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -1710,40 +1710,40 @@
         <v>1</v>
       </c>
       <c r="D14" s="5">
-        <v>53.491100000000003</v>
+        <v>93.745999999999995</v>
       </c>
       <c r="E14" s="5">
-        <v>53.843299999999999</v>
+        <v>93.637100000000004</v>
       </c>
       <c r="F14" s="5">
-        <v>55.208799999999997</v>
+        <v>93.522800000000004</v>
       </c>
       <c r="G14" s="5">
-        <v>55.418300000000002</v>
+        <v>93.804199999999994</v>
       </c>
       <c r="H14" s="5">
-        <v>56.148200000000003</v>
+        <v>94.056600000000003</v>
       </c>
       <c r="I14" s="5">
-        <v>56.917000000000002</v>
+        <v>93.958200000000005</v>
       </c>
       <c r="J14" s="5">
-        <v>52.643999999999998</v>
+        <v>94.086600000000004</v>
       </c>
       <c r="K14" s="5">
-        <v>52.297800000000002</v>
+        <v>93.849500000000006</v>
       </c>
       <c r="L14" s="5">
-        <v>50.1738</v>
+        <v>93.614900000000006</v>
       </c>
       <c r="M14" s="5">
-        <v>49.018999999999998</v>
+        <v>96.545100000000005</v>
       </c>
       <c r="N14" s="5">
-        <v>47.8461</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+        <v>94.190899999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1754,40 +1754,40 @@
         <v>1</v>
       </c>
       <c r="D15" s="5">
-        <v>43.700099999999999</v>
+        <v>91.431200000000004</v>
       </c>
       <c r="E15" s="5">
-        <v>43.8583</v>
+        <v>86.150800000000004</v>
       </c>
       <c r="F15" s="5">
-        <v>44.404600000000002</v>
+        <v>89.316000000000003</v>
       </c>
       <c r="G15" s="5">
-        <v>44.304900000000004</v>
+        <v>87.673299999999998</v>
       </c>
       <c r="H15" s="5">
-        <v>45.064799999999998</v>
+        <v>99.216200000000001</v>
       </c>
       <c r="I15" s="5">
-        <v>46.133400000000002</v>
+        <v>87.617199999999997</v>
       </c>
       <c r="J15" s="5">
-        <v>43.0931</v>
+        <v>85.373999999999995</v>
       </c>
       <c r="K15" s="5">
-        <v>42.8596</v>
+        <v>89.499200000000002</v>
       </c>
       <c r="L15" s="5">
-        <v>41.809399999999997</v>
+        <v>89.4452</v>
       </c>
       <c r="M15" s="5">
-        <v>40.456099999999999</v>
+        <v>82.683400000000006</v>
       </c>
       <c r="N15" s="5">
-        <v>39.711500000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+        <v>81.818700000000007</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -1798,40 +1798,40 @@
         <v>1</v>
       </c>
       <c r="D16" s="5">
-        <v>51.040199999999999</v>
+        <v>83.944100000000006</v>
       </c>
       <c r="E16" s="5">
-        <v>52.585599999999999</v>
+        <v>85.384</v>
       </c>
       <c r="F16" s="5">
-        <v>52.829099999999997</v>
+        <v>86.100399999999993</v>
       </c>
       <c r="G16" s="5">
-        <v>52.871000000000002</v>
+        <v>88.585499999999996</v>
       </c>
       <c r="H16" s="5">
-        <v>53.700600000000001</v>
+        <v>89.682199999999995</v>
       </c>
       <c r="I16" s="5">
-        <v>54.241100000000003</v>
+        <v>91.343500000000006</v>
       </c>
       <c r="J16" s="5">
-        <v>50.247300000000003</v>
+        <v>85.046899999999994</v>
       </c>
       <c r="K16" s="5">
-        <v>50.304000000000002</v>
+        <v>84.977599999999995</v>
       </c>
       <c r="L16" s="5">
-        <v>48.303100000000001</v>
+        <v>84.689400000000006</v>
       </c>
       <c r="M16" s="5">
-        <v>47.2239</v>
+        <v>80.644800000000004</v>
       </c>
       <c r="N16" s="5">
-        <v>45.528500000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+        <v>79.560199999999995</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1842,40 +1842,40 @@
         <v>1</v>
       </c>
       <c r="D17" s="5">
-        <v>34.260899999999999</v>
+        <v>84.869900000000001</v>
       </c>
       <c r="E17" s="5">
-        <v>34.953099999999999</v>
+        <v>86.205500000000001</v>
       </c>
       <c r="F17" s="5">
-        <v>34.957299999999996</v>
+        <v>87.677700000000002</v>
       </c>
       <c r="G17" s="5">
-        <v>35.323</v>
+        <v>89.560900000000004</v>
       </c>
       <c r="H17" s="5">
-        <v>35.471600000000002</v>
+        <v>91.566500000000005</v>
       </c>
       <c r="I17" s="5">
-        <v>35.583300000000001</v>
+        <v>92.302199999999999</v>
       </c>
       <c r="J17" s="5">
-        <v>33.768799999999999</v>
+        <v>83.322999999999993</v>
       </c>
       <c r="K17" s="5">
-        <v>33.142400000000002</v>
+        <v>82.666399999999996</v>
       </c>
       <c r="L17" s="5">
-        <v>32.377899999999997</v>
+        <v>79.733199999999997</v>
       </c>
       <c r="M17" s="5">
-        <v>31.658000000000001</v>
+        <v>78.160399999999996</v>
       </c>
       <c r="N17" s="5">
-        <v>30.62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+        <v>77.275099999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -1886,40 +1886,40 @@
         <v>1</v>
       </c>
       <c r="D18" s="5">
-        <v>29.233000000000001</v>
+        <v>88.615600000000001</v>
       </c>
       <c r="E18" s="5">
-        <v>30.3687</v>
+        <v>89.416600000000003</v>
       </c>
       <c r="F18" s="5">
-        <v>30.956600000000002</v>
+        <v>88.905699999999996</v>
       </c>
       <c r="G18" s="5">
-        <v>32.212400000000002</v>
+        <v>89.410200000000003</v>
       </c>
       <c r="H18" s="5">
-        <v>32.7545</v>
+        <v>89.4529</v>
       </c>
       <c r="I18" s="5">
-        <v>33.560899999999997</v>
+        <v>89.333399999999997</v>
       </c>
       <c r="J18" s="5">
-        <v>28.4742</v>
+        <v>88.5655</v>
       </c>
       <c r="K18" s="5">
-        <v>28.261299999999999</v>
+        <v>88.896000000000001</v>
       </c>
       <c r="L18" s="5">
-        <v>27.690999999999999</v>
+        <v>87.242400000000004</v>
       </c>
       <c r="M18" s="5">
-        <v>26.792400000000001</v>
+        <v>86.911000000000001</v>
       </c>
       <c r="N18" s="5">
-        <v>25.770199999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+        <v>85.299800000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -1930,40 +1930,40 @@
         <v>1</v>
       </c>
       <c r="D19" s="5">
-        <v>75.007000000000005</v>
+        <v>55.942500000000003</v>
       </c>
       <c r="E19" s="5">
-        <v>76.789299999999997</v>
+        <v>52.428699999999999</v>
       </c>
       <c r="F19" s="5">
-        <v>77.578500000000005</v>
+        <v>81.733999999999995</v>
       </c>
       <c r="G19" s="5">
-        <v>77.895799999999994</v>
+        <v>53.761800000000001</v>
       </c>
       <c r="H19" s="5">
-        <v>78.028599999999997</v>
+        <v>53.164400000000001</v>
       </c>
       <c r="I19" s="5">
-        <v>79.328400000000002</v>
+        <v>53.448500000000003</v>
       </c>
       <c r="J19" s="5">
-        <v>75.837299999999999</v>
+        <v>52.419800000000002</v>
       </c>
       <c r="K19" s="5">
-        <v>75.232200000000006</v>
+        <v>53.775700000000001</v>
       </c>
       <c r="L19" s="5">
-        <v>73.045699999999997</v>
+        <v>54.843499999999999</v>
       </c>
       <c r="M19" s="5">
-        <v>73.2637</v>
+        <v>54.445399999999999</v>
       </c>
       <c r="N19" s="5">
-        <v>72.489000000000004</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+        <v>51.391800000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1974,40 +1974,40 @@
         <v>1</v>
       </c>
       <c r="D20" s="5">
-        <v>55.8157</v>
+        <v>90.096299999999999</v>
       </c>
       <c r="E20" s="5">
-        <v>56.860700000000001</v>
+        <v>90.748000000000005</v>
       </c>
       <c r="F20" s="5">
-        <v>57.374099999999999</v>
+        <v>96.985299999999995</v>
       </c>
       <c r="G20" s="5">
-        <v>58.363500000000002</v>
+        <v>100.292</v>
       </c>
       <c r="H20" s="5">
-        <v>59.417099999999998</v>
+        <v>101.854</v>
       </c>
       <c r="I20" s="5">
-        <v>60.581299999999999</v>
+        <v>103.655</v>
       </c>
       <c r="J20" s="5">
-        <v>55.994</v>
+        <v>106.73099999999999</v>
       </c>
       <c r="K20" s="5">
-        <v>55.422800000000002</v>
+        <v>81.361500000000007</v>
       </c>
       <c r="L20" s="5">
-        <v>50.786799999999999</v>
+        <v>85.190899999999999</v>
       </c>
       <c r="M20" s="5">
-        <v>48.902000000000001</v>
+        <v>112.81399999999999</v>
       </c>
       <c r="N20" s="5">
-        <v>49.041200000000003</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+        <v>80.559799999999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -2018,40 +2018,40 @@
         <v>1</v>
       </c>
       <c r="D21" s="5">
-        <v>55.925800000000002</v>
+        <v>96.850099999999998</v>
       </c>
       <c r="E21" s="5">
-        <v>56.425899999999999</v>
+        <v>90.689899999999994</v>
       </c>
       <c r="F21" s="5">
-        <v>56.875999999999998</v>
+        <v>94.571899999999999</v>
       </c>
       <c r="G21" s="5">
-        <v>57.5762</v>
+        <v>106.056</v>
       </c>
       <c r="H21" s="5">
-        <v>57.803199999999997</v>
+        <v>101.143</v>
       </c>
       <c r="I21" s="5">
-        <v>58.452399999999997</v>
+        <v>94.116799999999998</v>
       </c>
       <c r="J21" s="5">
-        <v>55.448599999999999</v>
+        <v>90.433400000000006</v>
       </c>
       <c r="K21" s="5">
-        <v>55.350700000000003</v>
+        <v>82.295000000000002</v>
       </c>
       <c r="L21" s="5">
-        <v>54.809699999999999</v>
+        <v>85.735900000000001</v>
       </c>
       <c r="M21" s="5">
-        <v>53.631100000000004</v>
+        <v>103.396</v>
       </c>
       <c r="N21" s="5">
-        <v>53.204300000000003</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+        <v>107.047</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -2062,40 +2062,40 @@
         <v>1</v>
       </c>
       <c r="D22" s="5">
-        <v>84.778000000000006</v>
+        <v>127.288</v>
       </c>
       <c r="E22" s="5">
-        <v>84.995900000000006</v>
+        <v>126.432</v>
       </c>
       <c r="F22" s="5">
-        <v>85.390199999999993</v>
+        <v>128.12899999999999</v>
       </c>
       <c r="G22" s="5">
-        <v>86.313199999999995</v>
+        <v>128.047</v>
       </c>
       <c r="H22" s="5">
-        <v>88.671999999999997</v>
+        <v>127.806</v>
       </c>
       <c r="I22" s="5">
-        <v>91.170400000000001</v>
+        <v>128.268</v>
       </c>
       <c r="J22" s="5">
-        <v>84.330399999999997</v>
+        <v>125.505</v>
       </c>
       <c r="K22" s="5">
-        <v>83.590900000000005</v>
+        <v>125.79900000000001</v>
       </c>
       <c r="L22" s="5">
-        <v>80.347800000000007</v>
+        <v>97.871899999999997</v>
       </c>
       <c r="M22" s="5">
-        <v>78.546300000000002</v>
+        <v>92.9345</v>
       </c>
       <c r="N22" s="5">
-        <v>74.835899999999995</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+        <v>90.883300000000006</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -2106,40 +2106,40 @@
         <v>1</v>
       </c>
       <c r="D23" s="5">
-        <v>47.314799999999998</v>
+        <v>88.978300000000004</v>
       </c>
       <c r="E23" s="5">
-        <v>47.500900000000001</v>
+        <v>88.662000000000006</v>
       </c>
       <c r="F23" s="5">
-        <v>48.6783</v>
+        <v>88.625500000000002</v>
       </c>
       <c r="G23" s="5">
-        <v>47.821300000000001</v>
+        <v>88.505899999999997</v>
       </c>
       <c r="H23" s="5">
-        <v>50.859299999999998</v>
+        <v>88.861599999999996</v>
       </c>
       <c r="I23" s="5">
-        <v>54.664200000000001</v>
+        <v>89.504400000000004</v>
       </c>
       <c r="J23" s="5">
-        <v>46.565199999999997</v>
+        <v>89.166899999999998</v>
       </c>
       <c r="K23" s="5">
-        <v>44.390300000000003</v>
+        <v>88.593699999999998</v>
       </c>
       <c r="L23" s="5">
-        <v>40.983800000000002</v>
+        <v>88.899199999999993</v>
       </c>
       <c r="M23" s="5">
-        <v>35.4587</v>
+        <v>88.015000000000001</v>
       </c>
       <c r="N23" s="5">
-        <v>32.472000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+        <v>86.705799999999996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -2150,40 +2150,40 @@
         <v>1</v>
       </c>
       <c r="D24" s="5">
-        <v>40.206000000000003</v>
+        <v>65.467500000000001</v>
       </c>
       <c r="E24" s="5">
-        <v>39.7286</v>
+        <v>65.747500000000002</v>
       </c>
       <c r="F24" s="5">
-        <v>40.7271</v>
+        <v>65.868499999999997</v>
       </c>
       <c r="G24" s="5">
-        <v>40.213700000000003</v>
+        <v>66.114099999999993</v>
       </c>
       <c r="H24" s="5">
-        <v>41.315399999999997</v>
+        <v>66.243499999999997</v>
       </c>
       <c r="I24" s="5">
-        <v>41.523899999999998</v>
+        <v>66.283500000000004</v>
       </c>
       <c r="J24" s="5">
-        <v>39.691299999999998</v>
+        <v>65.865099999999998</v>
       </c>
       <c r="K24" s="5">
-        <v>39.228999999999999</v>
+        <v>64.837299999999999</v>
       </c>
       <c r="L24" s="5">
-        <v>39.040700000000001</v>
+        <v>64.8339</v>
       </c>
       <c r="M24" s="5">
-        <v>39.456099999999999</v>
+        <v>63.868600000000001</v>
       </c>
       <c r="N24" s="5">
-        <v>38.372100000000003</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+        <v>62.8566</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -2194,40 +2194,40 @@
         <v>1</v>
       </c>
       <c r="D25" s="5">
-        <v>58.566800000000001</v>
+        <v>126.405</v>
       </c>
       <c r="E25" s="5">
-        <v>60.430500000000002</v>
+        <v>126.581</v>
       </c>
       <c r="F25" s="5">
-        <v>61.293999999999997</v>
+        <v>126.688</v>
       </c>
       <c r="G25" s="5">
-        <v>61.662500000000001</v>
+        <v>126.211</v>
       </c>
       <c r="H25" s="5">
-        <v>62.838999999999999</v>
+        <v>125.913</v>
       </c>
       <c r="I25" s="5">
-        <v>64.008300000000006</v>
+        <v>125.57</v>
       </c>
       <c r="J25" s="5">
-        <v>59.391300000000001</v>
+        <v>126.334</v>
       </c>
       <c r="K25" s="5">
-        <v>58.545000000000002</v>
+        <v>126.41</v>
       </c>
       <c r="L25" s="5">
-        <v>55.950899999999997</v>
+        <v>126.974</v>
       </c>
       <c r="M25" s="5">
-        <v>55.261499999999998</v>
+        <v>127.17700000000001</v>
       </c>
       <c r="N25" s="5">
-        <v>53.544499999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+        <v>127.07299999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -2238,40 +2238,40 @@
         <v>1</v>
       </c>
       <c r="D26" s="5">
-        <v>58.278500000000001</v>
+        <v>94.475200000000001</v>
       </c>
       <c r="E26" s="5">
-        <v>58.567900000000002</v>
+        <v>106.306</v>
       </c>
       <c r="F26" s="5">
-        <v>59.175600000000003</v>
+        <v>96.779600000000002</v>
       </c>
       <c r="G26" s="5">
-        <v>59.7515</v>
+        <v>110.884</v>
       </c>
       <c r="H26" s="5">
-        <v>60.392099999999999</v>
+        <v>121.953</v>
       </c>
       <c r="I26" s="5">
-        <v>60.532899999999998</v>
+        <v>117.79</v>
       </c>
       <c r="J26" s="5">
-        <v>57.7042</v>
+        <v>95.409400000000005</v>
       </c>
       <c r="K26" s="5">
-        <v>57.495399999999997</v>
+        <v>95.618899999999996</v>
       </c>
       <c r="L26" s="5">
-        <v>55.657699999999998</v>
+        <v>104.68600000000001</v>
       </c>
       <c r="M26" s="5">
-        <v>55.394500000000001</v>
+        <v>94.697000000000003</v>
       </c>
       <c r="N26" s="5">
-        <v>54.436100000000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+        <v>93.240499999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
         <v>41</v>
       </c>
@@ -2282,40 +2282,40 @@
         <v>1</v>
       </c>
       <c r="D27" s="5">
-        <v>82.169399999999996</v>
+        <v>121.86199999999999</v>
       </c>
       <c r="E27" s="5">
-        <v>83.910600000000002</v>
+        <v>122.41</v>
       </c>
       <c r="F27" s="5">
-        <v>85.287499999999994</v>
+        <v>122.30800000000001</v>
       </c>
       <c r="G27" s="5">
-        <v>87.274100000000004</v>
+        <v>122.42100000000001</v>
       </c>
       <c r="H27" s="5">
-        <v>89.438400000000001</v>
+        <v>124.047</v>
       </c>
       <c r="I27" s="5">
-        <v>92.436400000000006</v>
+        <v>122.83799999999999</v>
       </c>
       <c r="J27" s="5">
-        <v>81.430400000000006</v>
+        <v>122.297</v>
       </c>
       <c r="K27" s="5">
-        <v>80.800799999999995</v>
+        <v>122.943</v>
       </c>
       <c r="L27" s="5">
-        <v>79.107600000000005</v>
+        <v>122.139</v>
       </c>
       <c r="M27" s="5">
-        <v>77.335999999999999</v>
+        <v>121.825</v>
       </c>
       <c r="N27" s="5">
-        <v>76.170599999999993</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+        <v>122.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -2326,40 +2326,40 @@
         <v>1</v>
       </c>
       <c r="D28" s="5">
-        <v>48.878300000000003</v>
+        <v>106.139</v>
       </c>
       <c r="E28" s="5">
-        <v>49.368499999999997</v>
+        <v>99.737099999999998</v>
       </c>
       <c r="F28" s="5">
-        <v>50.31</v>
+        <v>89.450900000000004</v>
       </c>
       <c r="G28" s="5">
-        <v>51.037399999999998</v>
+        <v>104.32899999999999</v>
       </c>
       <c r="H28" s="5">
-        <v>51.179699999999997</v>
+        <v>113.879</v>
       </c>
       <c r="I28" s="5">
-        <v>51.833599999999997</v>
+        <v>121.3</v>
       </c>
       <c r="J28" s="5">
-        <v>48.481299999999997</v>
+        <v>97.913300000000007</v>
       </c>
       <c r="K28" s="5">
-        <v>48.279899999999998</v>
+        <v>90.916200000000003</v>
       </c>
       <c r="L28" s="5">
-        <v>47.671700000000001</v>
+        <v>98.337100000000007</v>
       </c>
       <c r="M28" s="5">
-        <v>48.231900000000003</v>
+        <v>99.773700000000005</v>
       </c>
       <c r="N28" s="5">
-        <v>46.7072</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+        <v>90.054299999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -2370,40 +2370,40 @@
         <v>1</v>
       </c>
       <c r="D29" s="5">
-        <v>98.800399999999996</v>
+        <v>97.332800000000006</v>
       </c>
       <c r="E29" s="5">
-        <v>99.938800000000001</v>
+        <v>100.005</v>
       </c>
       <c r="F29" s="5">
-        <v>100.10599999999999</v>
+        <v>98.292000000000002</v>
       </c>
       <c r="G29" s="5">
-        <v>100.227</v>
+        <v>106.255</v>
       </c>
       <c r="H29" s="5">
-        <v>100.247</v>
+        <v>166.85400000000001</v>
       </c>
       <c r="I29" s="5">
-        <v>100.535</v>
+        <v>126.307</v>
       </c>
       <c r="J29" s="5">
-        <v>99.709500000000006</v>
+        <v>96.773700000000005</v>
       </c>
       <c r="K29" s="5">
-        <v>99.7149</v>
+        <v>98.200100000000006</v>
       </c>
       <c r="L29" s="5">
-        <v>99.27</v>
+        <v>97.777199999999993</v>
       </c>
       <c r="M29" s="5">
-        <v>98.723600000000005</v>
+        <v>98.223399999999998</v>
       </c>
       <c r="N29" s="5">
-        <v>98.385099999999994</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+        <v>91.924800000000005</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -2414,40 +2414,40 @@
         <v>1</v>
       </c>
       <c r="D30" s="5">
-        <v>77.434700000000007</v>
+        <v>85.323099999999997</v>
       </c>
       <c r="E30" s="5">
-        <v>77.773300000000006</v>
+        <v>84.680899999999994</v>
       </c>
       <c r="F30" s="5">
-        <v>77.787999999999997</v>
+        <v>87.1614</v>
       </c>
       <c r="G30" s="5">
-        <v>78.888499999999993</v>
+        <v>115.935</v>
       </c>
       <c r="H30" s="5">
-        <v>79.8215</v>
+        <v>90.444999999999993</v>
       </c>
       <c r="I30" s="5">
-        <v>80.817899999999995</v>
+        <v>110.36799999999999</v>
       </c>
       <c r="J30" s="5">
-        <v>76.864699999999999</v>
+        <v>84.624099999999999</v>
       </c>
       <c r="K30" s="5">
-        <v>76.192800000000005</v>
+        <v>98.918400000000005</v>
       </c>
       <c r="L30" s="5">
-        <v>75.187399999999997</v>
+        <v>90.604900000000001</v>
       </c>
       <c r="M30" s="5">
-        <v>74.161600000000007</v>
+        <v>122.631</v>
       </c>
       <c r="N30" s="5">
-        <v>72.876099999999994</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+        <v>103.527</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
         <v>45</v>
       </c>
@@ -2458,40 +2458,40 @@
         <v>1</v>
       </c>
       <c r="D31" s="5">
-        <v>45.098399999999998</v>
+        <v>71.350999999999999</v>
       </c>
       <c r="E31" s="5">
-        <v>45.493400000000001</v>
+        <v>68.390600000000006</v>
       </c>
       <c r="F31" s="5">
-        <v>45.5227</v>
+        <v>68.145300000000006</v>
       </c>
       <c r="G31" s="5">
-        <v>45.763399999999997</v>
+        <v>75.126599999999996</v>
       </c>
       <c r="H31" s="5">
-        <v>46.1723</v>
+        <v>72.758899999999997</v>
       </c>
       <c r="I31" s="5">
-        <v>46.048900000000003</v>
+        <v>70.725200000000001</v>
       </c>
       <c r="J31" s="5">
-        <v>45.657600000000002</v>
+        <v>71.08</v>
       </c>
       <c r="K31" s="5">
-        <v>45.4788</v>
+        <v>70.690700000000007</v>
       </c>
       <c r="L31" s="5">
-        <v>45.661999999999999</v>
+        <v>70.9405</v>
       </c>
       <c r="M31" s="5">
-        <v>44.016100000000002</v>
+        <v>70.271900000000002</v>
       </c>
       <c r="N31" s="5">
-        <v>43.850299999999997</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+        <v>71.165099999999995</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -2502,40 +2502,40 @@
         <v>1</v>
       </c>
       <c r="D32" s="5">
-        <v>60.516599999999997</v>
+        <v>114.947</v>
       </c>
       <c r="E32" s="5">
-        <v>61.645299999999999</v>
+        <v>116.15600000000001</v>
       </c>
       <c r="F32" s="5">
-        <v>62.482100000000003</v>
+        <v>116.01600000000001</v>
       </c>
       <c r="G32" s="5">
-        <v>64.161900000000003</v>
+        <v>116.078</v>
       </c>
       <c r="H32" s="5">
-        <v>64.614900000000006</v>
+        <v>117.319</v>
       </c>
       <c r="I32" s="5">
-        <v>65.279200000000003</v>
+        <v>117.042</v>
       </c>
       <c r="J32" s="5">
-        <v>60.448500000000003</v>
+        <v>114.502</v>
       </c>
       <c r="K32" s="5">
-        <v>60.227899999999998</v>
+        <v>114.616</v>
       </c>
       <c r="L32" s="5">
-        <v>59.955300000000001</v>
+        <v>114.63200000000001</v>
       </c>
       <c r="M32" s="5">
-        <v>58.318600000000004</v>
+        <v>112.69799999999999</v>
       </c>
       <c r="N32" s="5">
-        <v>55.2851</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+        <v>106.68600000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -2546,40 +2546,40 @@
         <v>1</v>
       </c>
       <c r="D33" s="5">
-        <v>25.666499999999999</v>
+        <v>85.0899</v>
       </c>
       <c r="E33" s="5">
-        <v>26.8506</v>
+        <v>85.894099999999995</v>
       </c>
       <c r="F33" s="5">
-        <v>27.3218</v>
+        <v>86.672499999999999</v>
       </c>
       <c r="G33" s="5">
-        <v>28.8369</v>
+        <v>87.677199999999999</v>
       </c>
       <c r="H33" s="5">
-        <v>29.9727</v>
+        <v>87.995099999999994</v>
       </c>
       <c r="I33" s="5">
-        <v>30.728200000000001</v>
+        <v>88.120999999999995</v>
       </c>
       <c r="J33" s="5">
-        <v>24.9755</v>
+        <v>84.455299999999994</v>
       </c>
       <c r="K33" s="5">
-        <v>24.414999999999999</v>
+        <v>83.963499999999996</v>
       </c>
       <c r="L33" s="5">
-        <v>22.782599999999999</v>
+        <v>83.233099999999993</v>
       </c>
       <c r="M33" s="5">
-        <v>20.3185</v>
+        <v>79.457899999999995</v>
       </c>
       <c r="N33" s="5">
-        <v>18.405899999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+        <v>78.336600000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -2590,40 +2590,40 @@
         <v>1</v>
       </c>
       <c r="D34" s="5">
-        <v>61.325000000000003</v>
+        <v>131.66300000000001</v>
       </c>
       <c r="E34" s="5">
-        <v>61.653399999999998</v>
+        <v>133.32300000000001</v>
       </c>
       <c r="F34" s="5">
-        <v>62.152099999999997</v>
+        <v>134.101</v>
       </c>
       <c r="G34" s="5">
-        <v>60.876600000000003</v>
+        <v>133.95400000000001</v>
       </c>
       <c r="H34" s="5">
-        <v>61.424500000000002</v>
+        <v>134.06200000000001</v>
       </c>
       <c r="I34" s="5">
-        <v>61.828699999999998</v>
+        <v>134.45500000000001</v>
       </c>
       <c r="J34" s="5">
-        <v>61.721800000000002</v>
+        <v>130.125</v>
       </c>
       <c r="K34" s="5">
-        <v>62.023000000000003</v>
+        <v>127.143</v>
       </c>
       <c r="L34" s="5">
-        <v>60.781199999999998</v>
+        <v>97.304599999999994</v>
       </c>
       <c r="M34" s="5">
-        <v>61.311300000000003</v>
+        <v>101.16800000000001</v>
       </c>
       <c r="N34" s="5">
-        <v>56.7181</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+        <v>94.014399999999995</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -2634,40 +2634,40 @@
         <v>1</v>
       </c>
       <c r="D35" s="5">
-        <v>57.508099999999999</v>
+        <v>89.039000000000001</v>
       </c>
       <c r="E35" s="5">
-        <v>59.196599999999997</v>
+        <v>88.6267</v>
       </c>
       <c r="F35" s="5">
-        <v>61.445700000000002</v>
+        <v>88.656199999999998</v>
       </c>
       <c r="G35" s="5">
-        <v>63.241100000000003</v>
+        <v>88.831599999999995</v>
       </c>
       <c r="H35" s="5">
-        <v>65.835400000000007</v>
+        <v>88.451300000000003</v>
       </c>
       <c r="I35" s="5">
-        <v>67.747</v>
+        <v>88.302999999999997</v>
       </c>
       <c r="J35" s="5">
-        <v>56.199599999999997</v>
+        <v>93.056299999999993</v>
       </c>
       <c r="K35" s="5">
-        <v>55.278300000000002</v>
+        <v>89.221199999999996</v>
       </c>
       <c r="L35" s="5">
-        <v>52.691299999999998</v>
+        <v>90.079700000000003</v>
       </c>
       <c r="M35" s="5">
-        <v>50.618299999999998</v>
+        <v>91.455600000000004</v>
       </c>
       <c r="N35" s="5">
-        <v>49.579900000000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+        <v>91.468100000000007</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -2678,40 +2678,40 @@
         <v>1</v>
       </c>
       <c r="D36" s="5">
-        <v>83.450199999999995</v>
+        <v>99.999700000000004</v>
       </c>
       <c r="E36" s="5">
-        <v>84.149500000000003</v>
+        <v>141.81800000000001</v>
       </c>
       <c r="F36" s="5">
-        <v>84.5304</v>
+        <v>141.87200000000001</v>
       </c>
       <c r="G36" s="5">
-        <v>85.695499999999996</v>
+        <v>141.744</v>
       </c>
       <c r="H36" s="5">
-        <v>87.188500000000005</v>
+        <v>141.96899999999999</v>
       </c>
       <c r="I36" s="5">
-        <v>89.854200000000006</v>
+        <v>142.24600000000001</v>
       </c>
       <c r="J36" s="5">
-        <v>82.58</v>
+        <v>115.21299999999999</v>
       </c>
       <c r="K36" s="5">
-        <v>82.230900000000005</v>
+        <v>97.947100000000006</v>
       </c>
       <c r="L36" s="5">
-        <v>79.847499999999997</v>
+        <v>92.142200000000003</v>
       </c>
       <c r="M36" s="5">
-        <v>77.060100000000006</v>
+        <v>91.924899999999994</v>
       </c>
       <c r="N36" s="5">
-        <v>75.178600000000003</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+        <v>104.503</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -2722,40 +2722,40 @@
         <v>1</v>
       </c>
       <c r="D37" s="5">
-        <v>61.4208</v>
+        <v>84.421899999999994</v>
       </c>
       <c r="E37" s="5">
-        <v>61.201700000000002</v>
+        <v>85.953299999999999</v>
       </c>
       <c r="F37" s="5">
-        <v>61.364899999999999</v>
+        <v>86.5321</v>
       </c>
       <c r="G37" s="5">
-        <v>60.563099999999999</v>
+        <v>119.91500000000001</v>
       </c>
       <c r="H37" s="5">
-        <v>60.909799999999997</v>
+        <v>90.365300000000005</v>
       </c>
       <c r="I37" s="5">
-        <v>60.895699999999998</v>
+        <v>95.132199999999997</v>
       </c>
       <c r="J37" s="5">
-        <v>61.268999999999998</v>
+        <v>88.772599999999997</v>
       </c>
       <c r="K37" s="5">
-        <v>60.954500000000003</v>
+        <v>86.043599999999998</v>
       </c>
       <c r="L37" s="5">
-        <v>61.572600000000001</v>
+        <v>111.325</v>
       </c>
       <c r="M37" s="5">
-        <v>62.322600000000001</v>
+        <v>84.730500000000006</v>
       </c>
       <c r="N37" s="5">
-        <v>62.346800000000002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+        <v>102.863</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -2766,40 +2766,40 @@
         <v>1</v>
       </c>
       <c r="D38" s="5">
-        <v>83.131100000000004</v>
+        <v>95.177800000000005</v>
       </c>
       <c r="E38" s="5">
-        <v>84.034000000000006</v>
+        <v>119.666</v>
       </c>
       <c r="F38" s="5">
-        <v>83.926199999999994</v>
+        <v>109.92400000000001</v>
       </c>
       <c r="G38" s="5">
-        <v>83.652500000000003</v>
+        <v>199.489</v>
       </c>
       <c r="H38" s="5">
-        <v>84.421400000000006</v>
+        <v>179.011</v>
       </c>
       <c r="I38" s="5">
-        <v>86.355599999999995</v>
+        <v>197.01499999999999</v>
       </c>
       <c r="J38" s="5">
-        <v>81.935500000000005</v>
+        <v>98.5244</v>
       </c>
       <c r="K38" s="5">
-        <v>81.526200000000003</v>
+        <v>104.379</v>
       </c>
       <c r="L38" s="5">
-        <v>77.740700000000004</v>
+        <v>110.459</v>
       </c>
       <c r="M38" s="5">
-        <v>74.633700000000005</v>
+        <v>108.087</v>
       </c>
       <c r="N38" s="5">
-        <v>71.446100000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+        <v>96.487300000000005</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -2810,40 +2810,40 @@
         <v>1</v>
       </c>
       <c r="D39" s="5">
-        <v>81.370800000000003</v>
+        <v>108.19799999999999</v>
       </c>
       <c r="E39" s="5">
-        <v>82.660700000000006</v>
+        <v>104.998</v>
       </c>
       <c r="F39" s="5">
-        <v>83.469200000000001</v>
+        <v>96.244900000000001</v>
       </c>
       <c r="G39" s="5">
-        <v>85.286299999999997</v>
+        <v>100.416</v>
       </c>
       <c r="H39" s="5">
-        <v>88.777199999999993</v>
+        <v>141.31299999999999</v>
       </c>
       <c r="I39" s="5">
-        <v>90.921999999999997</v>
+        <v>149.149</v>
       </c>
       <c r="J39" s="5">
-        <v>79.942800000000005</v>
+        <v>110.72199999999999</v>
       </c>
       <c r="K39" s="5">
-        <v>77.930999999999997</v>
+        <v>94.278199999999998</v>
       </c>
       <c r="L39" s="5">
-        <v>76.018100000000004</v>
+        <v>109.23</v>
       </c>
       <c r="M39" s="5">
-        <v>73.4405</v>
+        <v>107.018</v>
       </c>
       <c r="N39" s="5">
-        <v>71.863200000000006</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+        <v>86.974199999999996</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
         <v>53</v>
       </c>
@@ -2854,40 +2854,40 @@
         <v>1</v>
       </c>
       <c r="D40" s="5">
-        <v>32.166200000000003</v>
+        <v>84.965100000000007</v>
       </c>
       <c r="E40" s="5">
-        <v>33.504800000000003</v>
+        <v>85.490600000000001</v>
       </c>
       <c r="F40" s="5">
-        <v>34.300699999999999</v>
+        <v>86.102400000000003</v>
       </c>
       <c r="G40" s="5">
-        <v>35.992899999999999</v>
+        <v>87.135999999999996</v>
       </c>
       <c r="H40" s="5">
-        <v>37.420299999999997</v>
+        <v>87.637699999999995</v>
       </c>
       <c r="I40" s="5">
-        <v>38.571399999999997</v>
+        <v>88.108900000000006</v>
       </c>
       <c r="J40" s="5">
-        <v>31.248799999999999</v>
+        <v>84.538799999999995</v>
       </c>
       <c r="K40" s="5">
-        <v>30.352</v>
+        <v>85.228099999999998</v>
       </c>
       <c r="L40" s="5">
-        <v>28.418099999999999</v>
+        <v>83.073499999999996</v>
       </c>
       <c r="M40" s="5">
-        <v>25.420400000000001</v>
+        <v>81.450599999999994</v>
       </c>
       <c r="N40" s="5">
-        <v>22.407</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+        <v>78.882999999999996</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -2898,40 +2898,40 @@
         <v>1</v>
       </c>
       <c r="D41" s="5">
-        <v>105.474</v>
+        <v>187.95699999999999</v>
       </c>
       <c r="E41" s="5">
-        <v>107.44499999999999</v>
+        <v>187.45099999999999</v>
       </c>
       <c r="F41" s="5">
-        <v>107.66500000000001</v>
+        <v>238.43899999999999</v>
       </c>
       <c r="G41" s="5">
-        <v>108.087</v>
+        <v>190.79900000000001</v>
       </c>
       <c r="H41" s="5">
-        <v>108.48099999999999</v>
+        <v>187.63499999999999</v>
       </c>
       <c r="I41" s="5">
-        <v>109.218</v>
+        <v>189.13900000000001</v>
       </c>
       <c r="J41" s="5">
-        <v>107.279</v>
+        <v>189.83600000000001</v>
       </c>
       <c r="K41" s="5">
-        <v>107.136</v>
+        <v>188.69200000000001</v>
       </c>
       <c r="L41" s="5">
-        <v>106.345</v>
+        <v>190.58199999999999</v>
       </c>
       <c r="M41" s="5">
-        <v>106.202</v>
+        <v>116.373</v>
       </c>
       <c r="N41" s="5">
-        <v>105.59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+        <v>116.545</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
         <v>72</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>79.171899999999994</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
         <v>69</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>77.043999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
         <v>73</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>71.351500000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
         <v>74</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>64.131600000000006</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
         <v>55</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>57.379399999999997</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>53.710099999999997</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>67.699600000000004</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>75.0809</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>140.584</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -3371,7 +3371,7 @@
         <v>81.927999999999997</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>80.494900000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>75.637200000000007</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14">
       <c r="A54" t="s">
         <v>78</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>105.61499999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14">
       <c r="A55" t="s">
         <v>60</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>79.266999999999996</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>127.98399999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>90.975200000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -3679,7 +3679,7 @@
         <v>69.120199999999997</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>73.849299999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14">
       <c r="A60" t="s">
         <v>70</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>86.983999999999995</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14">
       <c r="A61" t="s">
         <v>65</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>74.488699999999994</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14">
       <c r="A62" t="s">
         <v>79</v>
       </c>
@@ -3855,7 +3855,7 @@
         <v>64.941999999999993</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>105.742</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14">
       <c r="A64" t="s">
         <v>80</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>61.881999999999998</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>79.239400000000003</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14">
       <c r="A66" t="s">
         <v>81</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>121.45</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14">
       <c r="A67" t="s">
         <v>67</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>113.47499999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14">
       <c r="A68" t="s">
         <v>82</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>64.321299999999994</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14">
       <c r="A69" t="s">
         <v>68</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>76.066900000000004</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14">
       <c r="A70" t="s">
         <v>83</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>76.156400000000005</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14">
       <c r="A71" t="s">
         <v>84</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>76.249499999999998</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14">
       <c r="A72" t="s">
         <v>85</v>
       </c>
@@ -4295,7 +4295,7 @@
         <v>93.434899999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14">
       <c r="A73" t="s">
         <v>86</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>119.627</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14">
       <c r="A74" t="s">
         <v>87</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>138.29300000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14">
       <c r="A75" t="s">
         <v>88</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>118.51600000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14">
       <c r="A76" t="s">
         <v>89</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>111.646</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14">
       <c r="A77" t="s">
         <v>90</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>74.681799999999996</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14">
       <c r="A78" t="s">
         <v>91</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>96.738299999999995</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14">
       <c r="A79" t="s">
         <v>92</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>100.65300000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14">
       <c r="A80" t="s">
         <v>93</v>
       </c>
@@ -4647,7 +4647,7 @@
         <v>64.720399999999998</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:14">
       <c r="A81" t="s">
         <v>94</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>133.20500000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14">
       <c r="A82" t="s">
         <v>95</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>105.816</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14">
       <c r="A83" t="s">
         <v>96</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>124.80800000000001</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:14">
       <c r="A84" t="s">
         <v>97</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>79.88</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:14">
       <c r="A85" t="s">
         <v>98</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>71.170100000000005</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:14">
       <c r="A86" t="s">
         <v>99</v>
       </c>
@@ -4911,7 +4911,7 @@
         <v>62.6083</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:14">
       <c r="A87" t="s">
         <v>100</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>88.314700000000002</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14">
       <c r="A88" t="s">
         <v>101</v>
       </c>
@@ -4999,7 +4999,7 @@
         <v>113.256</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:14">
       <c r="A89" t="s">
         <v>102</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>119.83</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:14">
       <c r="A90" t="s">
         <v>103</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>94.313999999999993</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:14">
       <c r="A91" t="s">
         <v>104</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>121.294</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:14">
       <c r="A92" t="s">
         <v>105</v>
       </c>
@@ -5175,7 +5175,7 @@
         <v>141.005</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:14">
       <c r="A93" t="s">
         <v>106</v>
       </c>
@@ -5219,7 +5219,7 @@
         <v>107.089</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:14">
       <c r="A94" t="s">
         <v>107</v>
       </c>
@@ -5263,7 +5263,7 @@
         <v>101.941</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:14">
       <c r="A95" t="s">
         <v>108</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>93.532200000000003</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:14">
       <c r="A96" t="s">
         <v>109</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>114.47199999999999</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:14">
       <c r="A97" t="s">
         <v>110</v>
       </c>
@@ -5395,7 +5395,7 @@
         <v>99.417900000000003</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:14">
       <c r="A98" t="s">
         <v>111</v>
       </c>
@@ -5439,7 +5439,7 @@
         <v>98.586799999999997</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:14">
       <c r="A99" t="s">
         <v>112</v>
       </c>
@@ -5483,7 +5483,7 @@
         <v>87.859300000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:14">
       <c r="A100" t="s">
         <v>113</v>
       </c>
@@ -5527,7 +5527,7 @@
         <v>77.058899999999994</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:14">
       <c r="A101" t="s">
         <v>114</v>
       </c>
@@ -5571,7 +5571,7 @@
         <v>106.467</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:14">
       <c r="A102" t="s">
         <v>115</v>
       </c>
@@ -5615,7 +5615,7 @@
         <v>60.877499999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:14">
       <c r="A103" t="s">
         <v>116</v>
       </c>
@@ -5659,7 +5659,7 @@
         <v>97.030799999999999</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:14">
       <c r="A104" t="s">
         <v>117</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>114.861</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:14">
       <c r="A105" t="s">
         <v>118</v>
       </c>
@@ -5747,7 +5747,7 @@
         <v>150.98699999999999</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:14">
       <c r="A106" t="s">
         <v>119</v>
       </c>
@@ -5791,7 +5791,7 @@
         <v>84.833399999999997</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:14">
       <c r="A107" t="s">
         <v>120</v>
       </c>
@@ -5835,7 +5835,7 @@
         <v>64.951700000000002</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:14">
       <c r="A108" t="s">
         <v>121</v>
       </c>
@@ -5879,7 +5879,7 @@
         <v>155.893</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:14">
       <c r="A109" t="s">
         <v>122</v>
       </c>
@@ -5923,7 +5923,7 @@
         <v>112.083</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:14">
       <c r="A110" t="s">
         <v>123</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>35.634500000000003</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:14">
       <c r="A111" t="s">
         <v>124</v>
       </c>
@@ -6011,7 +6011,7 @@
         <v>61.286700000000003</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:14">
       <c r="A112" t="s">
         <v>125</v>
       </c>
@@ -6055,7 +6055,7 @@
         <v>80.779200000000003</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:14">
       <c r="A113" t="s">
         <v>126</v>
       </c>
@@ -6099,7 +6099,7 @@
         <v>158.99100000000001</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:14">
       <c r="A114" t="s">
         <v>127</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>110.402</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:14">
       <c r="A115" t="s">
         <v>128</v>
       </c>
@@ -6187,7 +6187,7 @@
         <v>132.31200000000001</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:14">
       <c r="A116" t="s">
         <v>129</v>
       </c>
@@ -6231,7 +6231,7 @@
         <v>111.84</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:14">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>151.648</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:14">
       <c r="A118" t="s">
         <v>131</v>
       </c>
@@ -6319,7 +6319,7 @@
         <v>65.465699999999998</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:14">
       <c r="A119" t="s">
         <v>132</v>
       </c>
@@ -6363,7 +6363,7 @@
         <v>127.208</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:14">
       <c r="A120" t="s">
         <v>133</v>
       </c>
@@ -6407,7 +6407,7 @@
         <v>101.083</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:14">
       <c r="A121" t="s">
         <v>134</v>
       </c>
@@ -6451,7 +6451,7 @@
         <v>116.274</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:14">
       <c r="A122" t="s">
         <v>135</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>122.345</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:14">
       <c r="A123" t="s">
         <v>136</v>
       </c>
@@ -6539,7 +6539,7 @@
         <v>129.374</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:14">
       <c r="A124" t="s">
         <v>137</v>
       </c>
@@ -6583,7 +6583,7 @@
         <v>205.327</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:14">
       <c r="A125" t="s">
         <v>138</v>
       </c>
@@ -6627,7 +6627,7 @@
         <v>86.593500000000006</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:14">
       <c r="A126" t="s">
         <v>139</v>
       </c>
@@ -6671,7 +6671,7 @@
         <v>60.525300000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:14">
       <c r="A127" t="s">
         <v>140</v>
       </c>
@@ -6715,7 +6715,7 @@
         <v>188.90100000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:14">
       <c r="A128" t="s">
         <v>141</v>
       </c>
@@ -6759,7 +6759,7 @@
         <v>119.39</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:14">
       <c r="A129" t="s">
         <v>142</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>131.85</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:14">
       <c r="A130" t="s">
         <v>143</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>118.699</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:14">
       <c r="A131" t="s">
         <v>144</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>120.712</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:14">
       <c r="A132" t="s">
         <v>145</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>109.649</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:14">
       <c r="A133" t="s">
         <v>146</v>
       </c>
@@ -6979,7 +6979,7 @@
         <v>118.137</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:14">
       <c r="A134" t="s">
         <v>147</v>
       </c>
@@ -7023,7 +7023,7 @@
         <v>163.65299999999999</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:14">
       <c r="A135" t="s">
         <v>148</v>
       </c>
@@ -7067,7 +7067,7 @@
         <v>113.575</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:14">
       <c r="A136" t="s">
         <v>149</v>
       </c>
@@ -7111,7 +7111,7 @@
         <v>128.91</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:14">
       <c r="A137" t="s">
         <v>150</v>
       </c>
@@ -7155,7 +7155,7 @@
         <v>94.816199999999995</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:14">
       <c r="A138" t="s">
         <v>151</v>
       </c>
@@ -7199,7 +7199,7 @@
         <v>94.673400000000001</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:14">
       <c r="A139" t="s">
         <v>152</v>
       </c>
@@ -7243,7 +7243,7 @@
         <v>61.561700000000002</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:14">
       <c r="A140" t="s">
         <v>153</v>
       </c>
@@ -7287,7 +7287,7 @@
         <v>111.837</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:14">
       <c r="A141" t="s">
         <v>154</v>
       </c>
@@ -7331,7 +7331,7 @@
         <v>112.129</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:14">
       <c r="A142" t="s">
         <v>155</v>
       </c>
@@ -7375,7 +7375,7 @@
         <v>86.456299999999999</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:14">
       <c r="A143" t="s">
         <v>156</v>
       </c>
@@ -7419,7 +7419,7 @@
         <v>141.756</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:14">
       <c r="A144" t="s">
         <v>157</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>94.5809</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:14">
       <c r="A145" t="s">
         <v>158</v>
       </c>
@@ -7507,7 +7507,7 @@
         <v>83.295900000000003</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:14">
       <c r="A146" t="s">
         <v>159</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>97.751499999999993</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:14">
       <c r="A147" t="s">
         <v>160</v>
       </c>
@@ -7595,7 +7595,7 @@
         <v>124.209</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:14">
       <c r="A148" t="s">
         <v>161</v>
       </c>
@@ -7639,7 +7639,7 @@
         <v>114.22</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:14">
       <c r="A149" t="s">
         <v>162</v>
       </c>
@@ -7683,7 +7683,7 @@
         <v>73.703599999999994</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:14">
       <c r="A150" t="s">
         <v>163</v>
       </c>
@@ -7727,7 +7727,7 @@
         <v>106.755</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:14">
       <c r="A151" t="s">
         <v>164</v>
       </c>
@@ -7771,7 +7771,7 @@
         <v>136.53</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:14">
       <c r="A152" t="s">
         <v>165</v>
       </c>
@@ -7815,7 +7815,7 @@
         <v>113.375</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:14">
       <c r="A153" t="s">
         <v>166</v>
       </c>
@@ -7859,7 +7859,7 @@
         <v>82.441500000000005</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:14">
       <c r="A154" t="s">
         <v>167</v>
       </c>
@@ -7903,7 +7903,7 @@
         <v>162.65299999999999</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:14">
       <c r="A155" t="s">
         <v>168</v>
       </c>
@@ -7947,7 +7947,7 @@
         <v>120.13500000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:14">
       <c r="A156" t="s">
         <v>169</v>
       </c>
@@ -7991,7 +7991,7 @@
         <v>136.36099999999999</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:14">
       <c r="A157" t="s">
         <v>170</v>
       </c>
@@ -8035,7 +8035,7 @@
         <v>104.143</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:14">
       <c r="A158" t="s">
         <v>171</v>
       </c>
@@ -8079,7 +8079,7 @@
         <v>114.027</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:14">
       <c r="A159" t="s">
         <v>172</v>
       </c>
@@ -8123,7 +8123,7 @@
         <v>77.644900000000007</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:14">
       <c r="A160" t="s">
         <v>173</v>
       </c>
@@ -8167,7 +8167,7 @@
         <v>93.123800000000003</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:14">
       <c r="A161" t="s">
         <v>174</v>
       </c>
@@ -8221,7 +8221,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3078A25-5F18-4F5A-891E-A45BA706ED91}">
   <dimension ref="A1:S161"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
@@ -8231,7 +8231,7 @@
     <col min="12" max="14" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -8275,7 +8275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -8329,7 +8329,7 @@
         <v>108326.40000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -8383,7 +8383,7 @@
         <v>82118.400000000009</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -8437,7 +8437,7 @@
         <v>2854924.8000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -8491,7 +8491,7 @@
         <v>326726.40000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -8545,7 +8545,7 @@
         <v>3588748.8000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -8599,7 +8599,7 @@
         <v>478732.80000000005</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -8653,7 +8653,7 @@
         <v>134534.39999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -8707,7 +8707,7 @@
         <v>4864204.7999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -8761,7 +8761,7 @@
         <v>1689542.4000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -8815,7 +8815,7 @@
         <v>35401766.399999999</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -8869,7 +8869,7 @@
         <v>2376192</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -8923,7 +8923,7 @@
         <v>8529830.4000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>216652.80000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -9031,7 +9031,7 @@
         <v>1789132.8</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>17580326.400000002</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -9139,7 +9139,7 @@
         <v>21366508.800000001</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>111820.8</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -9247,7 +9247,7 @@
         <v>1292928</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>405350.40000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -9355,7 +9355,7 @@
         <v>1090252.8</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -9409,7 +9409,7 @@
         <v>2982470.4000000004</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -9463,7 +9463,7 @@
         <v>152006.39999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -9517,7 +9517,7 @@
         <v>12567609.600000001</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -9571,7 +9571,7 @@
         <v>391372.80000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -9625,7 +9625,7 @@
         <v>518918.40000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -9679,7 +9679,7 @@
         <v>232377.60000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>80371.200000000012</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -9787,7 +9787,7 @@
         <v>82118.400000000009</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
         <v>45</v>
       </c>
@@ -9841,7 +9841,7 @@
         <v>33196.800000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -9895,7 +9895,7 @@
         <v>17536646.400000002</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -9949,7 +9949,7 @@
         <v>2886374.4000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -10003,7 +10003,7 @@
         <v>4032537.6</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>1493856</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -10111,7 +10111,7 @@
         <v>1700025.6</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -10165,7 +10165,7 @@
         <v>377395.20000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
         <v>51</v>
       </c>
@@ -10219,7 +10219,7 @@
         <v>686649.60000000009</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
         <v>52</v>
       </c>
@@ -10273,7 +10273,7 @@
         <v>366912</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
         <v>53</v>
       </c>
@@ -10327,7 +10327,7 @@
         <v>3754732.8000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
         <v>54</v>
       </c>
@@ -10381,7 +10381,7 @@
         <v>1196832</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
         <v>72</v>
       </c>
@@ -10435,7 +10435,7 @@
         <v>7443229.2480000006</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
         <v>69</v>
       </c>
@@ -10489,7 +10489,7 @@
         <v>15058627.583999999</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
         <v>73</v>
       </c>
@@ -10543,7 +10543,7 @@
         <v>611939.3280000001</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
         <v>74</v>
       </c>
@@ -10597,7 +10597,7 @@
         <v>11939421.312000001</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
         <v>55</v>
       </c>
@@ -10651,7 +10651,7 @@
         <v>30148460.159999996</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
         <v>75</v>
       </c>
@@ -10705,7 +10705,7 @@
         <v>4801585.1519999998</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
         <v>76</v>
       </c>
@@ -10759,7 +10759,7 @@
         <v>4760141.568</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -10813,7 +10813,7 @@
         <v>973504.89599999995</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -10867,7 +10867,7 @@
         <v>1625752.128</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -10921,7 +10921,7 @@
         <v>1427235.2640000002</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -10975,7 +10975,7 @@
         <v>1607790.9120000002</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -11029,7 +11029,7 @@
         <v>1302188.1600000001</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14">
       <c r="A53" t="s">
         <v>78</v>
       </c>
@@ -11083,7 +11083,7 @@
         <v>112205.18400000001</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14">
       <c r="A54" t="s">
         <v>60</v>
       </c>
@@ -11137,7 +11137,7 @@
         <v>431436.09600000002</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14">
       <c r="A55" t="s">
         <v>61</v>
       </c>
@@ -11191,7 +11191,7 @@
         <v>317186.68800000002</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14">
       <c r="A56" t="s">
         <v>62</v>
       </c>
@@ -11245,7 +11245,7 @@
         <v>206536.51199999999</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14">
       <c r="A57" t="s">
         <v>63</v>
       </c>
@@ -11299,7 +11299,7 @@
         <v>19581918.720000003</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14">
       <c r="A58" t="s">
         <v>64</v>
       </c>
@@ -11353,7 +11353,7 @@
         <v>212214.91200000001</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14">
       <c r="A59" t="s">
         <v>70</v>
       </c>
@@ -11407,7 +11407,7 @@
         <v>6842699.1359999999</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -11461,7 +11461,7 @@
         <v>963248.83199999994</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14">
       <c r="A61" t="s">
         <v>79</v>
       </c>
@@ -11515,7 +11515,7 @@
         <v>3380919.3600000003</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14">
       <c r="A62" t="s">
         <v>71</v>
       </c>
@@ -11569,7 +11569,7 @@
         <v>730818.81599999999</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14">
       <c r="A63" t="s">
         <v>80</v>
       </c>
@@ -11623,7 +11623,7 @@
         <v>590413.82400000002</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -11677,7 +11677,7 @@
         <v>435192.576</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14">
       <c r="A65" t="s">
         <v>81</v>
       </c>
@@ -11731,7 +11731,7 @@
         <v>43348.031999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -11785,7 +11785,7 @@
         <v>323965.82400000002</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14">
       <c r="A67" t="s">
         <v>82</v>
       </c>
@@ -11839,7 +11839,7 @@
         <v>898340.35199999996</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14">
       <c r="A68" t="s">
         <v>68</v>
       </c>
@@ -11893,7 +11893,7 @@
         <v>234633235.20000002</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -11947,7 +11947,7 @@
         <v>865492.99200000009</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14">
       <c r="A70" t="s">
         <v>84</v>
       </c>
@@ -12001,7 +12001,7 @@
         <v>550612.60800000001</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14">
       <c r="A71" t="s">
         <v>85</v>
       </c>
@@ -12055,7 +12055,7 @@
         <v>9822863.2320000008</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14">
       <c r="A72" t="s">
         <v>86</v>
       </c>
@@ -12109,7 +12109,7 @@
         <v>11393893.056</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14">
       <c r="A73" t="s">
         <v>87</v>
       </c>
@@ -12163,7 +12163,7 @@
         <v>1063905.024</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14">
       <c r="A74" t="s">
         <v>88</v>
       </c>
@@ -12217,7 +12217,7 @@
         <v>383388.09600000002</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14">
       <c r="A75" t="s">
         <v>89</v>
       </c>
@@ -12271,7 +12271,7 @@
         <v>63370.94400000001</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14">
       <c r="A76" t="s">
         <v>90</v>
       </c>
@@ -12325,7 +12325,7 @@
         <v>307183968</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14">
       <c r="A77" t="s">
         <v>91</v>
       </c>
@@ -12379,7 +12379,7 @@
         <v>32465422.080000002</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14">
       <c r="A78" t="s">
         <v>92</v>
       </c>
@@ -12433,7 +12433,7 @@
         <v>134879472</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14">
       <c r="A79" t="s">
         <v>93</v>
       </c>
@@ -12487,7 +12487,7 @@
         <v>6337863.1680000005</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -12541,7 +12541,7 @@
         <v>5690298.432</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:14">
       <c r="A81" t="s">
         <v>95</v>
       </c>
@@ -12595,7 +12595,7 @@
         <v>13181995.008000001</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14">
       <c r="A82" t="s">
         <v>96</v>
       </c>
@@ -12649,7 +12649,7 @@
         <v>1238397.888</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14">
       <c r="A83" t="s">
         <v>97</v>
       </c>
@@ -12703,7 +12703,7 @@
         <v>40666080</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:14">
       <c r="A84" t="s">
         <v>98</v>
       </c>
@@ -12757,7 +12757,7 @@
         <v>5222922.432</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:14">
       <c r="A85" t="s">
         <v>99</v>
       </c>
@@ -12811,7 +12811,7 @@
         <v>233845.24800000002</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:14">
       <c r="A86" t="s">
         <v>100</v>
       </c>
@@ -12865,7 +12865,7 @@
         <v>737964.86400000006</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:14">
       <c r="A87" t="s">
         <v>101</v>
       </c>
@@ -12919,7 +12919,7 @@
         <v>49229107.200000003</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14">
       <c r="A88" t="s">
         <v>102</v>
       </c>
@@ -12973,7 +12973,7 @@
         <v>2900317.0559999999</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:14">
       <c r="A89" t="s">
         <v>103</v>
       </c>
@@ -13027,7 +13027,7 @@
         <v>515336.63999999996</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:14">
       <c r="A90" t="s">
         <v>104</v>
       </c>
@@ -13081,7 +13081,7 @@
         <v>494789.56799999997</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:14">
       <c r="A91" t="s">
         <v>105</v>
       </c>
@@ -13135,7 +13135,7 @@
         <v>2313432.5759999999</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:14">
       <c r="A92" t="s">
         <v>106</v>
       </c>
@@ -13189,7 +13189,7 @@
         <v>1781025.7920000004</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:14">
       <c r="A93" t="s">
         <v>107</v>
       </c>
@@ -13243,7 +13243,7 @@
         <v>413265.21600000001</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:14">
       <c r="A94" t="s">
         <v>108</v>
       </c>
@@ -13297,7 +13297,7 @@
         <v>10201481.472000001</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:14">
       <c r="A95" t="s">
         <v>109</v>
       </c>
@@ -13351,7 +13351,7 @@
         <v>993283.20000000007</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:14">
       <c r="A96" t="s">
         <v>110</v>
       </c>
@@ -13405,7 +13405,7 @@
         <v>2350368.3840000001</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:14">
       <c r="A97" t="s">
         <v>111</v>
       </c>
@@ -13459,7 +13459,7 @@
         <v>9480010.1760000009</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:14">
       <c r="A98" t="s">
         <v>112</v>
       </c>
@@ -13513,7 +13513,7 @@
         <v>10786828.416000001</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:14">
       <c r="A99" t="s">
         <v>113</v>
       </c>
@@ -13567,7 +13567,7 @@
         <v>659655.3600000001</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:14">
       <c r="A100" t="s">
         <v>114</v>
       </c>
@@ -13621,7 +13621,7 @@
         <v>4915170.6240000008</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:14">
       <c r="A101" t="s">
         <v>115</v>
       </c>
@@ -13675,7 +13675,7 @@
         <v>40388974.080000006</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:14">
       <c r="A102" t="s">
         <v>116</v>
       </c>
@@ -13729,7 +13729,7 @@
         <v>22815461.760000002</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:14">
       <c r="A103" t="s">
         <v>117</v>
       </c>
@@ -13783,7 +13783,7 @@
         <v>10866221.184</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:14">
       <c r="A104" t="s">
         <v>118</v>
       </c>
@@ -13837,7 +13837,7 @@
         <v>426998.20800000004</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:14">
       <c r="A105" t="s">
         <v>119</v>
       </c>
@@ -13891,7 +13891,7 @@
         <v>13849600.128</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:14">
       <c r="A106" t="s">
         <v>120</v>
       </c>
@@ -13945,7 +13945,7 @@
         <v>239401.34400000004</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:14">
       <c r="A107" t="s">
         <v>121</v>
       </c>
@@ -13999,7 +13999,7 @@
         <v>1238065.9200000002</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:14">
       <c r="A108" t="s">
         <v>122</v>
       </c>
@@ -14053,7 +14053,7 @@
         <v>22315413.120000005</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:14">
       <c r="A109" t="s">
         <v>123</v>
       </c>
@@ -14107,7 +14107,7 @@
         <v>2123337.216</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:14">
       <c r="A110" t="s">
         <v>124</v>
       </c>
@@ -14161,7 +14161,7 @@
         <v>1895187.8400000003</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:14">
       <c r="A111" t="s">
         <v>125</v>
       </c>
@@ -14215,7 +14215,7 @@
         <v>9926017.9199999999</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:14">
       <c r="A112" t="s">
         <v>126</v>
       </c>
@@ -14269,7 +14269,7 @@
         <v>576488.64</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:14">
       <c r="A113" t="s">
         <v>127</v>
       </c>
@@ -14323,7 +14323,7 @@
         <v>1346479.68</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:14">
       <c r="A114" t="s">
         <v>128</v>
       </c>
@@ -14377,7 +14377,7 @@
         <v>53866.176000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:14">
       <c r="A115" t="s">
         <v>129</v>
       </c>
@@ -14431,7 +14431,7 @@
         <v>330098.49600000004</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:14">
       <c r="A116" t="s">
         <v>130</v>
       </c>
@@ -14485,7 +14485,7 @@
         <v>366335.424</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:14">
       <c r="A117" t="s">
         <v>131</v>
       </c>
@@ -14539,7 +14539,7 @@
         <v>326918.59200000006</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:14">
       <c r="A118" t="s">
         <v>132</v>
       </c>
@@ -14593,7 +14593,7 @@
         <v>46702.656000000003</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:14">
       <c r="A119" t="s">
         <v>133</v>
       </c>
@@ -14647,7 +14647,7 @@
         <v>1294832.4480000001</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:14">
       <c r="A120" t="s">
         <v>134</v>
       </c>
@@ -14701,7 +14701,7 @@
         <v>839634.43200000003</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:14">
       <c r="A121" t="s">
         <v>135</v>
       </c>
@@ -14755,7 +14755,7 @@
         <v>1001477.5680000002</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:14">
       <c r="A122" t="s">
         <v>136</v>
       </c>
@@ -14809,7 +14809,7 @@
         <v>232447.48800000001</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:14">
       <c r="A123" t="s">
         <v>137</v>
       </c>
@@ -14863,7 +14863,7 @@
         <v>62567.232000000011</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:14">
       <c r="A124" t="s">
         <v>138</v>
       </c>
@@ -14917,7 +14917,7 @@
         <v>3117756.0960000004</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:14">
       <c r="A125" t="s">
         <v>139</v>
       </c>
@@ -14971,7 +14971,7 @@
         <v>7500886.8480000012</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:14">
       <c r="A126" t="s">
         <v>140</v>
       </c>
@@ -15025,7 +15025,7 @@
         <v>40832.064000000006</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:14">
       <c r="A127" t="s">
         <v>141</v>
       </c>
@@ -15079,7 +15079,7 @@
         <v>2065190.4000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:14">
       <c r="A128" t="s">
         <v>142</v>
       </c>
@@ -15133,7 +15133,7 @@
         <v>339079.10400000005</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:14">
       <c r="A129" t="s">
         <v>143</v>
       </c>
@@ -15187,7 +15187,7 @@
         <v>1440147.0720000002</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:14">
       <c r="A130" t="s">
         <v>144</v>
       </c>
@@ -15241,7 +15241,7 @@
         <v>294193.53600000002</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:14">
       <c r="A131" t="s">
         <v>145</v>
       </c>
@@ -15295,7 +15295,7 @@
         <v>38560.703999999998</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:14">
       <c r="A132" t="s">
         <v>146</v>
       </c>
@@ -15349,7 +15349,7 @@
         <v>30418.752000000004</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:14">
       <c r="A133" t="s">
         <v>147</v>
       </c>
@@ -15403,7 +15403,7 @@
         <v>227712.57600000003</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:14">
       <c r="A134" t="s">
         <v>148</v>
       </c>
@@ -15457,7 +15457,7 @@
         <v>2048032.8960000002</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:14">
       <c r="A135" t="s">
         <v>149</v>
       </c>
@@ -15511,7 +15511,7 @@
         <v>64716.288</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:14">
       <c r="A136" t="s">
         <v>150</v>
       </c>
@@ -15565,7 +15565,7 @@
         <v>777276.86400000006</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:14">
       <c r="A137" t="s">
         <v>151</v>
       </c>
@@ -15619,7 +15619,7 @@
         <v>46737.600000000006</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:14">
       <c r="A138" t="s">
         <v>152</v>
       </c>
@@ -15673,7 +15673,7 @@
         <v>2463377.2800000003</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:14">
       <c r="A139" t="s">
         <v>153</v>
       </c>
@@ -15727,7 +15727,7 @@
         <v>271672.12800000003</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:14">
       <c r="A140" t="s">
         <v>154</v>
       </c>
@@ -15781,7 +15781,7 @@
         <v>355310.59200000006</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:14">
       <c r="A141" t="s">
         <v>155</v>
       </c>
@@ -15835,7 +15835,7 @@
         <v>298736.25599999999</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:14">
       <c r="A142" t="s">
         <v>156</v>
       </c>
@@ -15889,7 +15889,7 @@
         <v>152705.28</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:14">
       <c r="A143" t="s">
         <v>157</v>
       </c>
@@ -15943,7 +15943,7 @@
         <v>234351.93599999999</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:14">
       <c r="A144" t="s">
         <v>158</v>
       </c>
@@ -15997,7 +15997,7 @@
         <v>227101.05599999998</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:19">
       <c r="A145" t="s">
         <v>159</v>
       </c>
@@ -16051,7 +16051,7 @@
         <v>277490.304</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:19">
       <c r="A146" t="s">
         <v>160</v>
       </c>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="S146" s="6"/>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:19">
       <c r="A147" t="s">
         <v>161</v>
       </c>
@@ -16160,7 +16160,7 @@
         <v>205470.72</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:19">
       <c r="A148" t="s">
         <v>162</v>
       </c>
@@ -16214,7 +16214,7 @@
         <v>637099.00800000003</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:19">
       <c r="A149" t="s">
         <v>163</v>
       </c>
@@ -16268,7 +16268,7 @@
         <v>512733.31199999992</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:19">
       <c r="A150" t="s">
         <v>164</v>
       </c>
@@ -16322,7 +16322,7 @@
         <v>77960.063999999998</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:19">
       <c r="A151" t="s">
         <v>165</v>
       </c>
@@ -16376,7 +16376,7 @@
         <v>135355.584</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:19">
       <c r="A152" t="s">
         <v>166</v>
       </c>
@@ -16430,7 +16430,7 @@
         <v>91710.528000000006</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:19">
       <c r="A153" t="s">
         <v>167</v>
       </c>
@@ -16484,7 +16484,7 @@
         <v>218644.60800000001</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:19">
       <c r="A154" t="s">
         <v>168</v>
       </c>
@@ -16538,7 +16538,7 @@
         <v>156147.26400000002</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:19">
       <c r="A155" t="s">
         <v>169</v>
       </c>
@@ -16592,7 +16592,7 @@
         <v>869354.304</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:19">
       <c r="A156" t="s">
         <v>170</v>
       </c>
@@ -16646,7 +16646,7 @@
         <v>1257896.6400000001</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:19">
       <c r="A157" t="s">
         <v>171</v>
       </c>
@@ -16700,7 +16700,7 @@
         <v>750474.81599999999</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:19">
       <c r="A158" t="s">
         <v>172</v>
       </c>
@@ -16754,7 +16754,7 @@
         <v>7794206.7840000009</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:19">
       <c r="A159" t="s">
         <v>173</v>
       </c>
@@ -16808,7 +16808,7 @@
         <v>393521.85599999997</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:19">
       <c r="A160" t="s">
         <v>174</v>
       </c>
@@ -16862,7 +16862,7 @@
         <v>486595.2</v>
       </c>
     </row>
-    <row r="161" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="161" spans="5:5">
       <c r="E161" s="1"/>
     </row>
   </sheetData>
@@ -16875,7 +16875,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B78385CA-3E61-4A82-8C62-F7714D6128D6}">
   <dimension ref="A1:N160"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
@@ -16885,7 +16885,7 @@
     <col min="12" max="14" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -16929,7 +16929,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -16983,7 +16983,7 @@
         <v>108326.40000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -17037,7 +17037,7 @@
         <v>82118.400000000009</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>2854924.8000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -17145,7 +17145,7 @@
         <v>326726.40000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -17199,7 +17199,7 @@
         <v>3588748.8000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -17253,7 +17253,7 @@
         <v>478732.80000000005</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -17307,7 +17307,7 @@
         <v>134534.39999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -17361,7 +17361,7 @@
         <v>4864204.7999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -17415,7 +17415,7 @@
         <v>1689542.4000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -17469,7 +17469,7 @@
         <v>35401766.399999999</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -17523,7 +17523,7 @@
         <v>2376192</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -17577,7 +17577,7 @@
         <v>8529830.4000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -17631,7 +17631,7 @@
         <v>216652.80000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -17685,7 +17685,7 @@
         <v>1789132.8</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -17739,7 +17739,7 @@
         <v>17580326.400000002</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -17793,7 +17793,7 @@
         <v>21366508.800000001</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -17847,7 +17847,7 @@
         <v>111820.8</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -17901,7 +17901,7 @@
         <v>1292928</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -17955,7 +17955,7 @@
         <v>405350.40000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -18009,7 +18009,7 @@
         <v>1090252.8</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -18063,7 +18063,7 @@
         <v>2982470.4000000004</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -18117,7 +18117,7 @@
         <v>152006.39999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -18171,7 +18171,7 @@
         <v>12567609.600000001</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -18225,7 +18225,7 @@
         <v>391372.80000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -18279,7 +18279,7 @@
         <v>518918.40000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -18333,7 +18333,7 @@
         <v>232377.60000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -18387,7 +18387,7 @@
         <v>80371.200000000012</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -18441,7 +18441,7 @@
         <v>82118.400000000009</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
         <v>45</v>
       </c>
@@ -18495,7 +18495,7 @@
         <v>33196.800000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -18549,7 +18549,7 @@
         <v>17536646.400000002</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -18603,7 +18603,7 @@
         <v>2886374.4000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -18657,7 +18657,7 @@
         <v>4032537.6</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -18711,7 +18711,7 @@
         <v>1493856</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -18765,7 +18765,7 @@
         <v>1700025.6</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -18819,7 +18819,7 @@
         <v>377395.20000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
         <v>51</v>
       </c>
@@ -18873,7 +18873,7 @@
         <v>686649.60000000009</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
         <v>52</v>
       </c>
@@ -18927,7 +18927,7 @@
         <v>366912</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
         <v>53</v>
       </c>
@@ -18981,7 +18981,7 @@
         <v>3754732.8000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
         <v>54</v>
       </c>
@@ -19035,7 +19035,7 @@
         <v>1196832</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
         <v>72</v>
       </c>
@@ -19089,7 +19089,7 @@
         <v>7443229.2480000006</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
         <v>69</v>
       </c>
@@ -19143,7 +19143,7 @@
         <v>15058627.583999999</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
         <v>73</v>
       </c>
@@ -19197,7 +19197,7 @@
         <v>611939.3280000001</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
         <v>74</v>
       </c>
@@ -19251,7 +19251,7 @@
         <v>11939421.312000001</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
         <v>55</v>
       </c>
@@ -19305,7 +19305,7 @@
         <v>30148460.159999996</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
         <v>75</v>
       </c>
@@ -19359,7 +19359,7 @@
         <v>4801585.1519999998</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
         <v>76</v>
       </c>
@@ -19413,7 +19413,7 @@
         <v>4760141.568</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -19467,7 +19467,7 @@
         <v>973504.89599999995</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -19521,7 +19521,7 @@
         <v>1625752.128</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -19575,7 +19575,7 @@
         <v>1427235.2640000002</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -19629,7 +19629,7 @@
         <v>1607790.9120000002</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -19683,7 +19683,7 @@
         <v>1302188.1600000001</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14">
       <c r="A53" t="s">
         <v>78</v>
       </c>
@@ -19737,7 +19737,7 @@
         <v>112205.18400000001</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14">
       <c r="A54" t="s">
         <v>60</v>
       </c>
@@ -19791,7 +19791,7 @@
         <v>431436.09600000002</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14">
       <c r="A55" t="s">
         <v>61</v>
       </c>
@@ -19845,7 +19845,7 @@
         <v>317186.68800000002</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14">
       <c r="A56" t="s">
         <v>62</v>
       </c>
@@ -19899,7 +19899,7 @@
         <v>206536.51199999999</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14">
       <c r="A57" t="s">
         <v>63</v>
       </c>
@@ -19953,7 +19953,7 @@
         <v>19581918.720000003</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14">
       <c r="A58" t="s">
         <v>64</v>
       </c>
@@ -20007,7 +20007,7 @@
         <v>212214.91200000001</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14">
       <c r="A59" t="s">
         <v>70</v>
       </c>
@@ -20061,7 +20061,7 @@
         <v>6842699.1359999999</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -20115,7 +20115,7 @@
         <v>963248.83199999994</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14">
       <c r="A61" t="s">
         <v>79</v>
       </c>
@@ -20169,7 +20169,7 @@
         <v>3380919.3600000003</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14">
       <c r="A62" t="s">
         <v>71</v>
       </c>
@@ -20223,7 +20223,7 @@
         <v>730818.81599999999</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14">
       <c r="A63" t="s">
         <v>80</v>
       </c>
@@ -20277,7 +20277,7 @@
         <v>590413.82400000002</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -20331,7 +20331,7 @@
         <v>435192.576</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14">
       <c r="A65" t="s">
         <v>81</v>
       </c>
@@ -20385,7 +20385,7 @@
         <v>43348.031999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -20439,7 +20439,7 @@
         <v>323965.82400000002</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14">
       <c r="A67" t="s">
         <v>82</v>
       </c>
@@ -20493,7 +20493,7 @@
         <v>898340.35199999996</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14">
       <c r="A68" t="s">
         <v>68</v>
       </c>
@@ -20547,7 +20547,7 @@
         <v>234633235.20000002</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -20601,7 +20601,7 @@
         <v>865492.99200000009</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14">
       <c r="A70" t="s">
         <v>84</v>
       </c>
@@ -20655,7 +20655,7 @@
         <v>550612.60800000001</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14">
       <c r="A71" t="s">
         <v>85</v>
       </c>
@@ -20709,7 +20709,7 @@
         <v>9822863.2320000008</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14">
       <c r="A72" t="s">
         <v>86</v>
       </c>
@@ -20763,7 +20763,7 @@
         <v>11393893.056</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14">
       <c r="A73" t="s">
         <v>87</v>
       </c>
@@ -20817,7 +20817,7 @@
         <v>1063905.024</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14">
       <c r="A74" t="s">
         <v>88</v>
       </c>
@@ -20871,7 +20871,7 @@
         <v>383388.09600000002</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14">
       <c r="A75" t="s">
         <v>89</v>
       </c>
@@ -20925,7 +20925,7 @@
         <v>63370.94400000001</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14">
       <c r="A76" t="s">
         <v>90</v>
       </c>
@@ -20979,7 +20979,7 @@
         <v>307183968</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14">
       <c r="A77" t="s">
         <v>91</v>
       </c>
@@ -21033,7 +21033,7 @@
         <v>32465422.080000002</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14">
       <c r="A78" t="s">
         <v>92</v>
       </c>
@@ -21087,7 +21087,7 @@
         <v>134879472</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14">
       <c r="A79" t="s">
         <v>93</v>
       </c>
@@ -21141,7 +21141,7 @@
         <v>6337863.1680000005</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14">
       <c r="A80" t="s">
         <v>94</v>
       </c>
@@ -21195,7 +21195,7 @@
         <v>5690298.432</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:14">
       <c r="A81" t="s">
         <v>95</v>
       </c>
@@ -21249,7 +21249,7 @@
         <v>13181995.008000001</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14">
       <c r="A82" t="s">
         <v>96</v>
       </c>
@@ -21303,7 +21303,7 @@
         <v>1238397.888</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14">
       <c r="A83" t="s">
         <v>97</v>
       </c>
@@ -21357,7 +21357,7 @@
         <v>40666080</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:14">
       <c r="A84" t="s">
         <v>98</v>
       </c>
@@ -21411,7 +21411,7 @@
         <v>5222922.432</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:14">
       <c r="A85" t="s">
         <v>99</v>
       </c>
@@ -21465,7 +21465,7 @@
         <v>233845.24800000002</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:14">
       <c r="A86" t="s">
         <v>100</v>
       </c>
@@ -21519,7 +21519,7 @@
         <v>737964.86400000006</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:14">
       <c r="A87" t="s">
         <v>101</v>
       </c>
@@ -21573,7 +21573,7 @@
         <v>49229107.200000003</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14">
       <c r="A88" t="s">
         <v>102</v>
       </c>
@@ -21627,7 +21627,7 @@
         <v>2900317.0559999999</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:14">
       <c r="A89" t="s">
         <v>103</v>
       </c>
@@ -21681,7 +21681,7 @@
         <v>515336.63999999996</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:14">
       <c r="A90" t="s">
         <v>104</v>
       </c>
@@ -21735,7 +21735,7 @@
         <v>494789.56799999997</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:14">
       <c r="A91" t="s">
         <v>105</v>
       </c>
@@ -21789,7 +21789,7 @@
         <v>2313432.5759999999</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:14">
       <c r="A92" t="s">
         <v>106</v>
       </c>
@@ -21843,7 +21843,7 @@
         <v>1781025.7920000004</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:14">
       <c r="A93" t="s">
         <v>107</v>
       </c>
@@ -21897,7 +21897,7 @@
         <v>413265.21600000001</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:14">
       <c r="A94" t="s">
         <v>108</v>
       </c>
@@ -21951,7 +21951,7 @@
         <v>10201481.472000001</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:14">
       <c r="A95" t="s">
         <v>109</v>
       </c>
@@ -22005,7 +22005,7 @@
         <v>993283.20000000007</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:14">
       <c r="A96" t="s">
         <v>110</v>
       </c>
@@ -22059,7 +22059,7 @@
         <v>2350368.3840000001</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:14">
       <c r="A97" t="s">
         <v>111</v>
       </c>
@@ -22113,7 +22113,7 @@
         <v>9480010.1760000009</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:14">
       <c r="A98" t="s">
         <v>112</v>
       </c>
@@ -22167,7 +22167,7 @@
         <v>10786828.416000001</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:14">
       <c r="A99" t="s">
         <v>113</v>
       </c>
@@ -22221,7 +22221,7 @@
         <v>659655.3600000001</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:14">
       <c r="A100" t="s">
         <v>114</v>
       </c>
@@ -22275,7 +22275,7 @@
         <v>4915170.6240000008</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:14">
       <c r="A101" t="s">
         <v>115</v>
       </c>
@@ -22329,7 +22329,7 @@
         <v>40388974.080000006</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:14">
       <c r="A102" t="s">
         <v>116</v>
       </c>
@@ -22383,7 +22383,7 @@
         <v>22815461.760000002</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:14">
       <c r="A103" t="s">
         <v>117</v>
       </c>
@@ -22437,7 +22437,7 @@
         <v>10866221.184</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:14">
       <c r="A104" t="s">
         <v>118</v>
       </c>
@@ -22491,7 +22491,7 @@
         <v>426998.20800000004</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:14">
       <c r="A105" t="s">
         <v>119</v>
       </c>
@@ -22545,7 +22545,7 @@
         <v>13849600.128</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:14">
       <c r="A106" t="s">
         <v>120</v>
       </c>
@@ -22599,7 +22599,7 @@
         <v>239401.34400000004</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:14">
       <c r="A107" t="s">
         <v>121</v>
       </c>
@@ -22653,7 +22653,7 @@
         <v>1238065.9200000002</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:14">
       <c r="A108" t="s">
         <v>122</v>
       </c>
@@ -22707,7 +22707,7 @@
         <v>22315413.120000005</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:14">
       <c r="A109" t="s">
         <v>123</v>
       </c>
@@ -22761,7 +22761,7 @@
         <v>2123337.216</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:14">
       <c r="A110" t="s">
         <v>124</v>
       </c>
@@ -22815,7 +22815,7 @@
         <v>1895187.8400000003</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:14">
       <c r="A111" t="s">
         <v>125</v>
       </c>
@@ -22869,7 +22869,7 @@
         <v>9926017.9199999999</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:14">
       <c r="A112" t="s">
         <v>126</v>
       </c>
@@ -22923,7 +22923,7 @@
         <v>576488.64</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:14">
       <c r="A113" t="s">
         <v>127</v>
       </c>
@@ -22977,7 +22977,7 @@
         <v>1346479.68</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:14">
       <c r="A114" t="s">
         <v>128</v>
       </c>
@@ -23031,7 +23031,7 @@
         <v>53866.176000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:14">
       <c r="A115" t="s">
         <v>129</v>
       </c>
@@ -23085,7 +23085,7 @@
         <v>330098.49600000004</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:14">
       <c r="A116" t="s">
         <v>130</v>
       </c>
@@ -23139,7 +23139,7 @@
         <v>366335.424</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:14">
       <c r="A117" t="s">
         <v>131</v>
       </c>
@@ -23193,7 +23193,7 @@
         <v>326918.59200000006</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:14">
       <c r="A118" t="s">
         <v>132</v>
       </c>
@@ -23247,7 +23247,7 @@
         <v>46702.656000000003</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:14">
       <c r="A119" t="s">
         <v>133</v>
       </c>
@@ -23301,7 +23301,7 @@
         <v>1294832.4480000001</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:14">
       <c r="A120" t="s">
         <v>134</v>
       </c>
@@ -23355,7 +23355,7 @@
         <v>839634.43200000003</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:14">
       <c r="A121" t="s">
         <v>135</v>
       </c>
@@ -23409,7 +23409,7 @@
         <v>1001477.5680000002</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:14">
       <c r="A122" t="s">
         <v>136</v>
       </c>
@@ -23463,7 +23463,7 @@
         <v>232447.48800000001</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:14">
       <c r="A123" t="s">
         <v>137</v>
       </c>
@@ -23517,7 +23517,7 @@
         <v>62567.232000000011</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:14">
       <c r="A124" t="s">
         <v>138</v>
       </c>
@@ -23571,7 +23571,7 @@
         <v>3117756.0960000004</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:14">
       <c r="A125" t="s">
         <v>139</v>
       </c>
@@ -23625,7 +23625,7 @@
         <v>7500886.8480000012</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:14">
       <c r="A126" t="s">
         <v>140</v>
       </c>
@@ -23679,7 +23679,7 @@
         <v>40832.064000000006</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:14">
       <c r="A127" t="s">
         <v>141</v>
       </c>
@@ -23733,7 +23733,7 @@
         <v>2065190.4000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:14">
       <c r="A128" t="s">
         <v>142</v>
       </c>
@@ -23787,7 +23787,7 @@
         <v>339079.10400000005</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:14">
       <c r="A129" t="s">
         <v>143</v>
       </c>
@@ -23841,7 +23841,7 @@
         <v>1440147.0720000002</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:14">
       <c r="A130" t="s">
         <v>144</v>
       </c>
@@ -23895,7 +23895,7 @@
         <v>294193.53600000002</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:14">
       <c r="A131" t="s">
         <v>145</v>
       </c>
@@ -23949,7 +23949,7 @@
         <v>38560.703999999998</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:14">
       <c r="A132" t="s">
         <v>146</v>
       </c>
@@ -24003,7 +24003,7 @@
         <v>30418.752000000004</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:14">
       <c r="A133" t="s">
         <v>147</v>
       </c>
@@ -24057,7 +24057,7 @@
         <v>227712.57600000003</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:14">
       <c r="A134" t="s">
         <v>148</v>
       </c>
@@ -24111,7 +24111,7 @@
         <v>2048032.8960000002</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:14">
       <c r="A135" t="s">
         <v>149</v>
       </c>
@@ -24165,7 +24165,7 @@
         <v>64716.288</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:14">
       <c r="A136" t="s">
         <v>150</v>
       </c>
@@ -24219,7 +24219,7 @@
         <v>777276.86400000006</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:14">
       <c r="A137" t="s">
         <v>151</v>
       </c>
@@ -24273,7 +24273,7 @@
         <v>46737.600000000006</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:14">
       <c r="A138" t="s">
         <v>152</v>
       </c>
@@ -24327,7 +24327,7 @@
         <v>2463377.2800000003</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:14">
       <c r="A139" t="s">
         <v>153</v>
       </c>
@@ -24381,7 +24381,7 @@
         <v>271672.12800000003</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:14">
       <c r="A140" t="s">
         <v>154</v>
       </c>
@@ -24435,7 +24435,7 @@
         <v>355310.59200000006</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:14">
       <c r="A141" t="s">
         <v>155</v>
       </c>
@@ -24489,7 +24489,7 @@
         <v>298736.25599999999</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:14">
       <c r="A142" t="s">
         <v>156</v>
       </c>
@@ -24543,7 +24543,7 @@
         <v>152705.28</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:14">
       <c r="A143" t="s">
         <v>157</v>
       </c>
@@ -24597,7 +24597,7 @@
         <v>234351.93599999999</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:14">
       <c r="A144" t="s">
         <v>158</v>
       </c>
@@ -24651,7 +24651,7 @@
         <v>227101.05599999998</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:14">
       <c r="A145" t="s">
         <v>159</v>
       </c>
@@ -24705,7 +24705,7 @@
         <v>277490.304</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:14">
       <c r="A146" t="s">
         <v>160</v>
       </c>
@@ -24759,7 +24759,7 @@
         <v>8180809.7280000001</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:14">
       <c r="A147" t="s">
         <v>161</v>
       </c>
@@ -24813,7 +24813,7 @@
         <v>205470.72</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:14">
       <c r="A148" t="s">
         <v>162</v>
       </c>
@@ -24867,7 +24867,7 @@
         <v>637099.00800000003</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:14">
       <c r="A149" t="s">
         <v>163</v>
       </c>
@@ -24921,7 +24921,7 @@
         <v>512733.31199999992</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:14">
       <c r="A150" t="s">
         <v>164</v>
       </c>
@@ -24975,7 +24975,7 @@
         <v>77960.063999999998</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:14">
       <c r="A151" t="s">
         <v>165</v>
       </c>
@@ -25029,7 +25029,7 @@
         <v>135355.584</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:14">
       <c r="A152" t="s">
         <v>166</v>
       </c>
@@ -25083,7 +25083,7 @@
         <v>91710.528000000006</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:14">
       <c r="A153" t="s">
         <v>167</v>
       </c>
@@ -25137,7 +25137,7 @@
         <v>218644.60800000001</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:14">
       <c r="A154" t="s">
         <v>168</v>
       </c>
@@ -25191,7 +25191,7 @@
         <v>156147.26400000002</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:14">
       <c r="A155" t="s">
         <v>169</v>
       </c>
@@ -25245,7 +25245,7 @@
         <v>869354.304</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:14">
       <c r="A156" t="s">
         <v>170</v>
       </c>
@@ -25299,7 +25299,7 @@
         <v>1257896.6400000001</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:14">
       <c r="A157" t="s">
         <v>171</v>
       </c>
@@ -25353,7 +25353,7 @@
         <v>750474.81599999999</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:14">
       <c r="A158" t="s">
         <v>172</v>
       </c>
@@ -25407,7 +25407,7 @@
         <v>7794206.7840000009</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:14">
       <c r="A159" t="s">
         <v>173</v>
       </c>
@@ -25461,7 +25461,7 @@
         <v>393521.85599999997</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:14">
       <c r="A160" t="s">
         <v>174</v>
       </c>
